--- a/excel/Cigarette Reconciliation.xlsx
+++ b/excel/Cigarette Reconciliation.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Daily'!$9:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Daily'!$A$1:$I$79</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Daily'!$A$1:$J$79</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Trends'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Trends'!$A$1:$R$124</definedName>
   </definedNames>
@@ -687,13 +687,14 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -816,35 +817,40 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
           <t>Closing</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Sold (counted)</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Sold (POS)</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>Variance RM</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>Item ID</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t>PLU</t>
         </is>
@@ -860,30 +866,34 @@
         <v/>
       </c>
       <c r="C10" s="15">
+        <f>IF(AND(ISNUMBER($L10),$L10&lt;&gt;""),INDEX(Data!$J:$J,$L10),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="15">
         <f>IF(AND(ISNUMBER($L10),$L10&lt;&gt;""),INDEX(Data!$K:$K,$L10),"")</f>
         <v/>
       </c>
-      <c r="D10" s="15">
+      <c r="E10" s="15">
         <f>IF(AND(ISNUMBER($L10),$L10&lt;&gt;""),IF(INDEX(Data!$L:$L,$L10)="","—",INDEX(Data!$L:$L,$L10)),"")</f>
         <v/>
       </c>
-      <c r="E10" s="15">
+      <c r="F10" s="15">
         <f>IF(AND(ISNUMBER($L10),$L10&lt;&gt;""),IF(INDEX(Data!$M:$M,$L10)="","—",INDEX(Data!$M:$M,$L10)),"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="G10" s="16">
         <f>IF(AND(ISNUMBER($L10),$L10&lt;&gt;""),IF(INDEX(Data!$N:$N,$L10)="","—",INDEX(Data!$N:$N,$L10)),"")</f>
         <v/>
       </c>
-      <c r="G10" s="17">
+      <c r="H10" s="17">
         <f>IF(AND(ISNUMBER($L10),$L10&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L10)="","—",INDEX(Data!$Q:$Q,$L10)),"")</f>
         <v/>
       </c>
-      <c r="H10" s="18">
+      <c r="I10" s="18">
         <f>IF(AND(ISNUMBER($L10),$L10&lt;&gt;""),INDEX(Data!$E:$E,$L10),"")</f>
         <v/>
       </c>
-      <c r="I10" s="18">
+      <c r="J10" s="18">
         <f>IF(AND(ISNUMBER($L10),$L10&lt;&gt;""),INDEX(Data!$F:$F,$L10),"")</f>
         <v/>
       </c>
@@ -902,30 +912,34 @@
         <v/>
       </c>
       <c r="C11" s="20">
+        <f>IF(AND(ISNUMBER($L11),$L11&lt;&gt;""),INDEX(Data!$J:$J,$L11),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="20">
         <f>IF(AND(ISNUMBER($L11),$L11&lt;&gt;""),INDEX(Data!$K:$K,$L11),"")</f>
         <v/>
       </c>
-      <c r="D11" s="20">
+      <c r="E11" s="20">
         <f>IF(AND(ISNUMBER($L11),$L11&lt;&gt;""),IF(INDEX(Data!$L:$L,$L11)="","—",INDEX(Data!$L:$L,$L11)),"")</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="F11" s="20">
         <f>IF(AND(ISNUMBER($L11),$L11&lt;&gt;""),IF(INDEX(Data!$M:$M,$L11)="","—",INDEX(Data!$M:$M,$L11)),"")</f>
         <v/>
       </c>
-      <c r="F11" s="21">
+      <c r="G11" s="21">
         <f>IF(AND(ISNUMBER($L11),$L11&lt;&gt;""),IF(INDEX(Data!$N:$N,$L11)="","—",INDEX(Data!$N:$N,$L11)),"")</f>
         <v/>
       </c>
-      <c r="G11" s="22">
+      <c r="H11" s="22">
         <f>IF(AND(ISNUMBER($L11),$L11&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L11)="","—",INDEX(Data!$Q:$Q,$L11)),"")</f>
         <v/>
       </c>
-      <c r="H11" s="23">
+      <c r="I11" s="23">
         <f>IF(AND(ISNUMBER($L11),$L11&lt;&gt;""),INDEX(Data!$E:$E,$L11),"")</f>
         <v/>
       </c>
-      <c r="I11" s="23">
+      <c r="J11" s="23">
         <f>IF(AND(ISNUMBER($L11),$L11&lt;&gt;""),INDEX(Data!$F:$F,$L11),"")</f>
         <v/>
       </c>
@@ -944,30 +958,34 @@
         <v/>
       </c>
       <c r="C12" s="15">
+        <f>IF(AND(ISNUMBER($L12),$L12&lt;&gt;""),INDEX(Data!$J:$J,$L12),"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="15">
         <f>IF(AND(ISNUMBER($L12),$L12&lt;&gt;""),INDEX(Data!$K:$K,$L12),"")</f>
         <v/>
       </c>
-      <c r="D12" s="15">
+      <c r="E12" s="15">
         <f>IF(AND(ISNUMBER($L12),$L12&lt;&gt;""),IF(INDEX(Data!$L:$L,$L12)="","—",INDEX(Data!$L:$L,$L12)),"")</f>
         <v/>
       </c>
-      <c r="E12" s="15">
+      <c r="F12" s="15">
         <f>IF(AND(ISNUMBER($L12),$L12&lt;&gt;""),IF(INDEX(Data!$M:$M,$L12)="","—",INDEX(Data!$M:$M,$L12)),"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="G12" s="16">
         <f>IF(AND(ISNUMBER($L12),$L12&lt;&gt;""),IF(INDEX(Data!$N:$N,$L12)="","—",INDEX(Data!$N:$N,$L12)),"")</f>
         <v/>
       </c>
-      <c r="G12" s="17">
+      <c r="H12" s="17">
         <f>IF(AND(ISNUMBER($L12),$L12&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L12)="","—",INDEX(Data!$Q:$Q,$L12)),"")</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="I12" s="18">
         <f>IF(AND(ISNUMBER($L12),$L12&lt;&gt;""),INDEX(Data!$E:$E,$L12),"")</f>
         <v/>
       </c>
-      <c r="I12" s="18">
+      <c r="J12" s="18">
         <f>IF(AND(ISNUMBER($L12),$L12&lt;&gt;""),INDEX(Data!$F:$F,$L12),"")</f>
         <v/>
       </c>
@@ -986,30 +1004,34 @@
         <v/>
       </c>
       <c r="C13" s="20">
+        <f>IF(AND(ISNUMBER($L13),$L13&lt;&gt;""),INDEX(Data!$J:$J,$L13),"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="20">
         <f>IF(AND(ISNUMBER($L13),$L13&lt;&gt;""),INDEX(Data!$K:$K,$L13),"")</f>
         <v/>
       </c>
-      <c r="D13" s="20">
+      <c r="E13" s="20">
         <f>IF(AND(ISNUMBER($L13),$L13&lt;&gt;""),IF(INDEX(Data!$L:$L,$L13)="","—",INDEX(Data!$L:$L,$L13)),"")</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="F13" s="20">
         <f>IF(AND(ISNUMBER($L13),$L13&lt;&gt;""),IF(INDEX(Data!$M:$M,$L13)="","—",INDEX(Data!$M:$M,$L13)),"")</f>
         <v/>
       </c>
-      <c r="F13" s="21">
+      <c r="G13" s="21">
         <f>IF(AND(ISNUMBER($L13),$L13&lt;&gt;""),IF(INDEX(Data!$N:$N,$L13)="","—",INDEX(Data!$N:$N,$L13)),"")</f>
         <v/>
       </c>
-      <c r="G13" s="22">
+      <c r="H13" s="22">
         <f>IF(AND(ISNUMBER($L13),$L13&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L13)="","—",INDEX(Data!$Q:$Q,$L13)),"")</f>
         <v/>
       </c>
-      <c r="H13" s="23">
+      <c r="I13" s="23">
         <f>IF(AND(ISNUMBER($L13),$L13&lt;&gt;""),INDEX(Data!$E:$E,$L13),"")</f>
         <v/>
       </c>
-      <c r="I13" s="23">
+      <c r="J13" s="23">
         <f>IF(AND(ISNUMBER($L13),$L13&lt;&gt;""),INDEX(Data!$F:$F,$L13),"")</f>
         <v/>
       </c>
@@ -1028,30 +1050,34 @@
         <v/>
       </c>
       <c r="C14" s="15">
+        <f>IF(AND(ISNUMBER($L14),$L14&lt;&gt;""),INDEX(Data!$J:$J,$L14),"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="15">
         <f>IF(AND(ISNUMBER($L14),$L14&lt;&gt;""),INDEX(Data!$K:$K,$L14),"")</f>
         <v/>
       </c>
-      <c r="D14" s="15">
+      <c r="E14" s="15">
         <f>IF(AND(ISNUMBER($L14),$L14&lt;&gt;""),IF(INDEX(Data!$L:$L,$L14)="","—",INDEX(Data!$L:$L,$L14)),"")</f>
         <v/>
       </c>
-      <c r="E14" s="15">
+      <c r="F14" s="15">
         <f>IF(AND(ISNUMBER($L14),$L14&lt;&gt;""),IF(INDEX(Data!$M:$M,$L14)="","—",INDEX(Data!$M:$M,$L14)),"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="G14" s="16">
         <f>IF(AND(ISNUMBER($L14),$L14&lt;&gt;""),IF(INDEX(Data!$N:$N,$L14)="","—",INDEX(Data!$N:$N,$L14)),"")</f>
         <v/>
       </c>
-      <c r="G14" s="17">
+      <c r="H14" s="17">
         <f>IF(AND(ISNUMBER($L14),$L14&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L14)="","—",INDEX(Data!$Q:$Q,$L14)),"")</f>
         <v/>
       </c>
-      <c r="H14" s="18">
+      <c r="I14" s="18">
         <f>IF(AND(ISNUMBER($L14),$L14&lt;&gt;""),INDEX(Data!$E:$E,$L14),"")</f>
         <v/>
       </c>
-      <c r="I14" s="18">
+      <c r="J14" s="18">
         <f>IF(AND(ISNUMBER($L14),$L14&lt;&gt;""),INDEX(Data!$F:$F,$L14),"")</f>
         <v/>
       </c>
@@ -1070,30 +1096,34 @@
         <v/>
       </c>
       <c r="C15" s="20">
+        <f>IF(AND(ISNUMBER($L15),$L15&lt;&gt;""),INDEX(Data!$J:$J,$L15),"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="20">
         <f>IF(AND(ISNUMBER($L15),$L15&lt;&gt;""),INDEX(Data!$K:$K,$L15),"")</f>
         <v/>
       </c>
-      <c r="D15" s="20">
+      <c r="E15" s="20">
         <f>IF(AND(ISNUMBER($L15),$L15&lt;&gt;""),IF(INDEX(Data!$L:$L,$L15)="","—",INDEX(Data!$L:$L,$L15)),"")</f>
         <v/>
       </c>
-      <c r="E15" s="20">
+      <c r="F15" s="20">
         <f>IF(AND(ISNUMBER($L15),$L15&lt;&gt;""),IF(INDEX(Data!$M:$M,$L15)="","—",INDEX(Data!$M:$M,$L15)),"")</f>
         <v/>
       </c>
-      <c r="F15" s="21">
+      <c r="G15" s="21">
         <f>IF(AND(ISNUMBER($L15),$L15&lt;&gt;""),IF(INDEX(Data!$N:$N,$L15)="","—",INDEX(Data!$N:$N,$L15)),"")</f>
         <v/>
       </c>
-      <c r="G15" s="22">
+      <c r="H15" s="22">
         <f>IF(AND(ISNUMBER($L15),$L15&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L15)="","—",INDEX(Data!$Q:$Q,$L15)),"")</f>
         <v/>
       </c>
-      <c r="H15" s="23">
+      <c r="I15" s="23">
         <f>IF(AND(ISNUMBER($L15),$L15&lt;&gt;""),INDEX(Data!$E:$E,$L15),"")</f>
         <v/>
       </c>
-      <c r="I15" s="23">
+      <c r="J15" s="23">
         <f>IF(AND(ISNUMBER($L15),$L15&lt;&gt;""),INDEX(Data!$F:$F,$L15),"")</f>
         <v/>
       </c>
@@ -1112,30 +1142,34 @@
         <v/>
       </c>
       <c r="C16" s="15">
+        <f>IF(AND(ISNUMBER($L16),$L16&lt;&gt;""),INDEX(Data!$J:$J,$L16),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="15">
         <f>IF(AND(ISNUMBER($L16),$L16&lt;&gt;""),INDEX(Data!$K:$K,$L16),"")</f>
         <v/>
       </c>
-      <c r="D16" s="15">
+      <c r="E16" s="15">
         <f>IF(AND(ISNUMBER($L16),$L16&lt;&gt;""),IF(INDEX(Data!$L:$L,$L16)="","—",INDEX(Data!$L:$L,$L16)),"")</f>
         <v/>
       </c>
-      <c r="E16" s="15">
+      <c r="F16" s="15">
         <f>IF(AND(ISNUMBER($L16),$L16&lt;&gt;""),IF(INDEX(Data!$M:$M,$L16)="","—",INDEX(Data!$M:$M,$L16)),"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="G16" s="16">
         <f>IF(AND(ISNUMBER($L16),$L16&lt;&gt;""),IF(INDEX(Data!$N:$N,$L16)="","—",INDEX(Data!$N:$N,$L16)),"")</f>
         <v/>
       </c>
-      <c r="G16" s="17">
+      <c r="H16" s="17">
         <f>IF(AND(ISNUMBER($L16),$L16&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L16)="","—",INDEX(Data!$Q:$Q,$L16)),"")</f>
         <v/>
       </c>
-      <c r="H16" s="18">
+      <c r="I16" s="18">
         <f>IF(AND(ISNUMBER($L16),$L16&lt;&gt;""),INDEX(Data!$E:$E,$L16),"")</f>
         <v/>
       </c>
-      <c r="I16" s="18">
+      <c r="J16" s="18">
         <f>IF(AND(ISNUMBER($L16),$L16&lt;&gt;""),INDEX(Data!$F:$F,$L16),"")</f>
         <v/>
       </c>
@@ -1154,30 +1188,34 @@
         <v/>
       </c>
       <c r="C17" s="20">
+        <f>IF(AND(ISNUMBER($L17),$L17&lt;&gt;""),INDEX(Data!$J:$J,$L17),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="20">
         <f>IF(AND(ISNUMBER($L17),$L17&lt;&gt;""),INDEX(Data!$K:$K,$L17),"")</f>
         <v/>
       </c>
-      <c r="D17" s="20">
+      <c r="E17" s="20">
         <f>IF(AND(ISNUMBER($L17),$L17&lt;&gt;""),IF(INDEX(Data!$L:$L,$L17)="","—",INDEX(Data!$L:$L,$L17)),"")</f>
         <v/>
       </c>
-      <c r="E17" s="20">
+      <c r="F17" s="20">
         <f>IF(AND(ISNUMBER($L17),$L17&lt;&gt;""),IF(INDEX(Data!$M:$M,$L17)="","—",INDEX(Data!$M:$M,$L17)),"")</f>
         <v/>
       </c>
-      <c r="F17" s="21">
+      <c r="G17" s="21">
         <f>IF(AND(ISNUMBER($L17),$L17&lt;&gt;""),IF(INDEX(Data!$N:$N,$L17)="","—",INDEX(Data!$N:$N,$L17)),"")</f>
         <v/>
       </c>
-      <c r="G17" s="22">
+      <c r="H17" s="22">
         <f>IF(AND(ISNUMBER($L17),$L17&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L17)="","—",INDEX(Data!$Q:$Q,$L17)),"")</f>
         <v/>
       </c>
-      <c r="H17" s="23">
+      <c r="I17" s="23">
         <f>IF(AND(ISNUMBER($L17),$L17&lt;&gt;""),INDEX(Data!$E:$E,$L17),"")</f>
         <v/>
       </c>
-      <c r="I17" s="23">
+      <c r="J17" s="23">
         <f>IF(AND(ISNUMBER($L17),$L17&lt;&gt;""),INDEX(Data!$F:$F,$L17),"")</f>
         <v/>
       </c>
@@ -1196,30 +1234,34 @@
         <v/>
       </c>
       <c r="C18" s="15">
+        <f>IF(AND(ISNUMBER($L18),$L18&lt;&gt;""),INDEX(Data!$J:$J,$L18),"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="15">
         <f>IF(AND(ISNUMBER($L18),$L18&lt;&gt;""),INDEX(Data!$K:$K,$L18),"")</f>
         <v/>
       </c>
-      <c r="D18" s="15">
+      <c r="E18" s="15">
         <f>IF(AND(ISNUMBER($L18),$L18&lt;&gt;""),IF(INDEX(Data!$L:$L,$L18)="","—",INDEX(Data!$L:$L,$L18)),"")</f>
         <v/>
       </c>
-      <c r="E18" s="15">
+      <c r="F18" s="15">
         <f>IF(AND(ISNUMBER($L18),$L18&lt;&gt;""),IF(INDEX(Data!$M:$M,$L18)="","—",INDEX(Data!$M:$M,$L18)),"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="G18" s="16">
         <f>IF(AND(ISNUMBER($L18),$L18&lt;&gt;""),IF(INDEX(Data!$N:$N,$L18)="","—",INDEX(Data!$N:$N,$L18)),"")</f>
         <v/>
       </c>
-      <c r="G18" s="17">
+      <c r="H18" s="17">
         <f>IF(AND(ISNUMBER($L18),$L18&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L18)="","—",INDEX(Data!$Q:$Q,$L18)),"")</f>
         <v/>
       </c>
-      <c r="H18" s="18">
+      <c r="I18" s="18">
         <f>IF(AND(ISNUMBER($L18),$L18&lt;&gt;""),INDEX(Data!$E:$E,$L18),"")</f>
         <v/>
       </c>
-      <c r="I18" s="18">
+      <c r="J18" s="18">
         <f>IF(AND(ISNUMBER($L18),$L18&lt;&gt;""),INDEX(Data!$F:$F,$L18),"")</f>
         <v/>
       </c>
@@ -1238,30 +1280,34 @@
         <v/>
       </c>
       <c r="C19" s="20">
+        <f>IF(AND(ISNUMBER($L19),$L19&lt;&gt;""),INDEX(Data!$J:$J,$L19),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="20">
         <f>IF(AND(ISNUMBER($L19),$L19&lt;&gt;""),INDEX(Data!$K:$K,$L19),"")</f>
         <v/>
       </c>
-      <c r="D19" s="20">
+      <c r="E19" s="20">
         <f>IF(AND(ISNUMBER($L19),$L19&lt;&gt;""),IF(INDEX(Data!$L:$L,$L19)="","—",INDEX(Data!$L:$L,$L19)),"")</f>
         <v/>
       </c>
-      <c r="E19" s="20">
+      <c r="F19" s="20">
         <f>IF(AND(ISNUMBER($L19),$L19&lt;&gt;""),IF(INDEX(Data!$M:$M,$L19)="","—",INDEX(Data!$M:$M,$L19)),"")</f>
         <v/>
       </c>
-      <c r="F19" s="21">
+      <c r="G19" s="21">
         <f>IF(AND(ISNUMBER($L19),$L19&lt;&gt;""),IF(INDEX(Data!$N:$N,$L19)="","—",INDEX(Data!$N:$N,$L19)),"")</f>
         <v/>
       </c>
-      <c r="G19" s="22">
+      <c r="H19" s="22">
         <f>IF(AND(ISNUMBER($L19),$L19&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L19)="","—",INDEX(Data!$Q:$Q,$L19)),"")</f>
         <v/>
       </c>
-      <c r="H19" s="23">
+      <c r="I19" s="23">
         <f>IF(AND(ISNUMBER($L19),$L19&lt;&gt;""),INDEX(Data!$E:$E,$L19),"")</f>
         <v/>
       </c>
-      <c r="I19" s="23">
+      <c r="J19" s="23">
         <f>IF(AND(ISNUMBER($L19),$L19&lt;&gt;""),INDEX(Data!$F:$F,$L19),"")</f>
         <v/>
       </c>
@@ -1280,30 +1326,34 @@
         <v/>
       </c>
       <c r="C20" s="15">
+        <f>IF(AND(ISNUMBER($L20),$L20&lt;&gt;""),INDEX(Data!$J:$J,$L20),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="15">
         <f>IF(AND(ISNUMBER($L20),$L20&lt;&gt;""),INDEX(Data!$K:$K,$L20),"")</f>
         <v/>
       </c>
-      <c r="D20" s="15">
+      <c r="E20" s="15">
         <f>IF(AND(ISNUMBER($L20),$L20&lt;&gt;""),IF(INDEX(Data!$L:$L,$L20)="","—",INDEX(Data!$L:$L,$L20)),"")</f>
         <v/>
       </c>
-      <c r="E20" s="15">
+      <c r="F20" s="15">
         <f>IF(AND(ISNUMBER($L20),$L20&lt;&gt;""),IF(INDEX(Data!$M:$M,$L20)="","—",INDEX(Data!$M:$M,$L20)),"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="G20" s="16">
         <f>IF(AND(ISNUMBER($L20),$L20&lt;&gt;""),IF(INDEX(Data!$N:$N,$L20)="","—",INDEX(Data!$N:$N,$L20)),"")</f>
         <v/>
       </c>
-      <c r="G20" s="17">
+      <c r="H20" s="17">
         <f>IF(AND(ISNUMBER($L20),$L20&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L20)="","—",INDEX(Data!$Q:$Q,$L20)),"")</f>
         <v/>
       </c>
-      <c r="H20" s="18">
+      <c r="I20" s="18">
         <f>IF(AND(ISNUMBER($L20),$L20&lt;&gt;""),INDEX(Data!$E:$E,$L20),"")</f>
         <v/>
       </c>
-      <c r="I20" s="18">
+      <c r="J20" s="18">
         <f>IF(AND(ISNUMBER($L20),$L20&lt;&gt;""),INDEX(Data!$F:$F,$L20),"")</f>
         <v/>
       </c>
@@ -1322,30 +1372,34 @@
         <v/>
       </c>
       <c r="C21" s="20">
+        <f>IF(AND(ISNUMBER($L21),$L21&lt;&gt;""),INDEX(Data!$J:$J,$L21),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="20">
         <f>IF(AND(ISNUMBER($L21),$L21&lt;&gt;""),INDEX(Data!$K:$K,$L21),"")</f>
         <v/>
       </c>
-      <c r="D21" s="20">
+      <c r="E21" s="20">
         <f>IF(AND(ISNUMBER($L21),$L21&lt;&gt;""),IF(INDEX(Data!$L:$L,$L21)="","—",INDEX(Data!$L:$L,$L21)),"")</f>
         <v/>
       </c>
-      <c r="E21" s="20">
+      <c r="F21" s="20">
         <f>IF(AND(ISNUMBER($L21),$L21&lt;&gt;""),IF(INDEX(Data!$M:$M,$L21)="","—",INDEX(Data!$M:$M,$L21)),"")</f>
         <v/>
       </c>
-      <c r="F21" s="21">
+      <c r="G21" s="21">
         <f>IF(AND(ISNUMBER($L21),$L21&lt;&gt;""),IF(INDEX(Data!$N:$N,$L21)="","—",INDEX(Data!$N:$N,$L21)),"")</f>
         <v/>
       </c>
-      <c r="G21" s="22">
+      <c r="H21" s="22">
         <f>IF(AND(ISNUMBER($L21),$L21&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L21)="","—",INDEX(Data!$Q:$Q,$L21)),"")</f>
         <v/>
       </c>
-      <c r="H21" s="23">
+      <c r="I21" s="23">
         <f>IF(AND(ISNUMBER($L21),$L21&lt;&gt;""),INDEX(Data!$E:$E,$L21),"")</f>
         <v/>
       </c>
-      <c r="I21" s="23">
+      <c r="J21" s="23">
         <f>IF(AND(ISNUMBER($L21),$L21&lt;&gt;""),INDEX(Data!$F:$F,$L21),"")</f>
         <v/>
       </c>
@@ -1364,30 +1418,34 @@
         <v/>
       </c>
       <c r="C22" s="15">
+        <f>IF(AND(ISNUMBER($L22),$L22&lt;&gt;""),INDEX(Data!$J:$J,$L22),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="15">
         <f>IF(AND(ISNUMBER($L22),$L22&lt;&gt;""),INDEX(Data!$K:$K,$L22),"")</f>
         <v/>
       </c>
-      <c r="D22" s="15">
+      <c r="E22" s="15">
         <f>IF(AND(ISNUMBER($L22),$L22&lt;&gt;""),IF(INDEX(Data!$L:$L,$L22)="","—",INDEX(Data!$L:$L,$L22)),"")</f>
         <v/>
       </c>
-      <c r="E22" s="15">
+      <c r="F22" s="15">
         <f>IF(AND(ISNUMBER($L22),$L22&lt;&gt;""),IF(INDEX(Data!$M:$M,$L22)="","—",INDEX(Data!$M:$M,$L22)),"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="G22" s="16">
         <f>IF(AND(ISNUMBER($L22),$L22&lt;&gt;""),IF(INDEX(Data!$N:$N,$L22)="","—",INDEX(Data!$N:$N,$L22)),"")</f>
         <v/>
       </c>
-      <c r="G22" s="17">
+      <c r="H22" s="17">
         <f>IF(AND(ISNUMBER($L22),$L22&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L22)="","—",INDEX(Data!$Q:$Q,$L22)),"")</f>
         <v/>
       </c>
-      <c r="H22" s="18">
+      <c r="I22" s="18">
         <f>IF(AND(ISNUMBER($L22),$L22&lt;&gt;""),INDEX(Data!$E:$E,$L22),"")</f>
         <v/>
       </c>
-      <c r="I22" s="18">
+      <c r="J22" s="18">
         <f>IF(AND(ISNUMBER($L22),$L22&lt;&gt;""),INDEX(Data!$F:$F,$L22),"")</f>
         <v/>
       </c>
@@ -1406,30 +1464,34 @@
         <v/>
       </c>
       <c r="C23" s="20">
+        <f>IF(AND(ISNUMBER($L23),$L23&lt;&gt;""),INDEX(Data!$J:$J,$L23),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="20">
         <f>IF(AND(ISNUMBER($L23),$L23&lt;&gt;""),INDEX(Data!$K:$K,$L23),"")</f>
         <v/>
       </c>
-      <c r="D23" s="20">
+      <c r="E23" s="20">
         <f>IF(AND(ISNUMBER($L23),$L23&lt;&gt;""),IF(INDEX(Data!$L:$L,$L23)="","—",INDEX(Data!$L:$L,$L23)),"")</f>
         <v/>
       </c>
-      <c r="E23" s="20">
+      <c r="F23" s="20">
         <f>IF(AND(ISNUMBER($L23),$L23&lt;&gt;""),IF(INDEX(Data!$M:$M,$L23)="","—",INDEX(Data!$M:$M,$L23)),"")</f>
         <v/>
       </c>
-      <c r="F23" s="21">
+      <c r="G23" s="21">
         <f>IF(AND(ISNUMBER($L23),$L23&lt;&gt;""),IF(INDEX(Data!$N:$N,$L23)="","—",INDEX(Data!$N:$N,$L23)),"")</f>
         <v/>
       </c>
-      <c r="G23" s="22">
+      <c r="H23" s="22">
         <f>IF(AND(ISNUMBER($L23),$L23&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L23)="","—",INDEX(Data!$Q:$Q,$L23)),"")</f>
         <v/>
       </c>
-      <c r="H23" s="23">
+      <c r="I23" s="23">
         <f>IF(AND(ISNUMBER($L23),$L23&lt;&gt;""),INDEX(Data!$E:$E,$L23),"")</f>
         <v/>
       </c>
-      <c r="I23" s="23">
+      <c r="J23" s="23">
         <f>IF(AND(ISNUMBER($L23),$L23&lt;&gt;""),INDEX(Data!$F:$F,$L23),"")</f>
         <v/>
       </c>
@@ -1448,30 +1510,34 @@
         <v/>
       </c>
       <c r="C24" s="15">
+        <f>IF(AND(ISNUMBER($L24),$L24&lt;&gt;""),INDEX(Data!$J:$J,$L24),"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="15">
         <f>IF(AND(ISNUMBER($L24),$L24&lt;&gt;""),INDEX(Data!$K:$K,$L24),"")</f>
         <v/>
       </c>
-      <c r="D24" s="15">
+      <c r="E24" s="15">
         <f>IF(AND(ISNUMBER($L24),$L24&lt;&gt;""),IF(INDEX(Data!$L:$L,$L24)="","—",INDEX(Data!$L:$L,$L24)),"")</f>
         <v/>
       </c>
-      <c r="E24" s="15">
+      <c r="F24" s="15">
         <f>IF(AND(ISNUMBER($L24),$L24&lt;&gt;""),IF(INDEX(Data!$M:$M,$L24)="","—",INDEX(Data!$M:$M,$L24)),"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="G24" s="16">
         <f>IF(AND(ISNUMBER($L24),$L24&lt;&gt;""),IF(INDEX(Data!$N:$N,$L24)="","—",INDEX(Data!$N:$N,$L24)),"")</f>
         <v/>
       </c>
-      <c r="G24" s="17">
+      <c r="H24" s="17">
         <f>IF(AND(ISNUMBER($L24),$L24&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L24)="","—",INDEX(Data!$Q:$Q,$L24)),"")</f>
         <v/>
       </c>
-      <c r="H24" s="18">
+      <c r="I24" s="18">
         <f>IF(AND(ISNUMBER($L24),$L24&lt;&gt;""),INDEX(Data!$E:$E,$L24),"")</f>
         <v/>
       </c>
-      <c r="I24" s="18">
+      <c r="J24" s="18">
         <f>IF(AND(ISNUMBER($L24),$L24&lt;&gt;""),INDEX(Data!$F:$F,$L24),"")</f>
         <v/>
       </c>
@@ -1490,30 +1556,34 @@
         <v/>
       </c>
       <c r="C25" s="20">
+        <f>IF(AND(ISNUMBER($L25),$L25&lt;&gt;""),INDEX(Data!$J:$J,$L25),"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="20">
         <f>IF(AND(ISNUMBER($L25),$L25&lt;&gt;""),INDEX(Data!$K:$K,$L25),"")</f>
         <v/>
       </c>
-      <c r="D25" s="20">
+      <c r="E25" s="20">
         <f>IF(AND(ISNUMBER($L25),$L25&lt;&gt;""),IF(INDEX(Data!$L:$L,$L25)="","—",INDEX(Data!$L:$L,$L25)),"")</f>
         <v/>
       </c>
-      <c r="E25" s="20">
+      <c r="F25" s="20">
         <f>IF(AND(ISNUMBER($L25),$L25&lt;&gt;""),IF(INDEX(Data!$M:$M,$L25)="","—",INDEX(Data!$M:$M,$L25)),"")</f>
         <v/>
       </c>
-      <c r="F25" s="21">
+      <c r="G25" s="21">
         <f>IF(AND(ISNUMBER($L25),$L25&lt;&gt;""),IF(INDEX(Data!$N:$N,$L25)="","—",INDEX(Data!$N:$N,$L25)),"")</f>
         <v/>
       </c>
-      <c r="G25" s="22">
+      <c r="H25" s="22">
         <f>IF(AND(ISNUMBER($L25),$L25&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L25)="","—",INDEX(Data!$Q:$Q,$L25)),"")</f>
         <v/>
       </c>
-      <c r="H25" s="23">
+      <c r="I25" s="23">
         <f>IF(AND(ISNUMBER($L25),$L25&lt;&gt;""),INDEX(Data!$E:$E,$L25),"")</f>
         <v/>
       </c>
-      <c r="I25" s="23">
+      <c r="J25" s="23">
         <f>IF(AND(ISNUMBER($L25),$L25&lt;&gt;""),INDEX(Data!$F:$F,$L25),"")</f>
         <v/>
       </c>
@@ -1532,30 +1602,34 @@
         <v/>
       </c>
       <c r="C26" s="15">
+        <f>IF(AND(ISNUMBER($L26),$L26&lt;&gt;""),INDEX(Data!$J:$J,$L26),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="15">
         <f>IF(AND(ISNUMBER($L26),$L26&lt;&gt;""),INDEX(Data!$K:$K,$L26),"")</f>
         <v/>
       </c>
-      <c r="D26" s="15">
+      <c r="E26" s="15">
         <f>IF(AND(ISNUMBER($L26),$L26&lt;&gt;""),IF(INDEX(Data!$L:$L,$L26)="","—",INDEX(Data!$L:$L,$L26)),"")</f>
         <v/>
       </c>
-      <c r="E26" s="15">
+      <c r="F26" s="15">
         <f>IF(AND(ISNUMBER($L26),$L26&lt;&gt;""),IF(INDEX(Data!$M:$M,$L26)="","—",INDEX(Data!$M:$M,$L26)),"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="G26" s="16">
         <f>IF(AND(ISNUMBER($L26),$L26&lt;&gt;""),IF(INDEX(Data!$N:$N,$L26)="","—",INDEX(Data!$N:$N,$L26)),"")</f>
         <v/>
       </c>
-      <c r="G26" s="17">
+      <c r="H26" s="17">
         <f>IF(AND(ISNUMBER($L26),$L26&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L26)="","—",INDEX(Data!$Q:$Q,$L26)),"")</f>
         <v/>
       </c>
-      <c r="H26" s="18">
+      <c r="I26" s="18">
         <f>IF(AND(ISNUMBER($L26),$L26&lt;&gt;""),INDEX(Data!$E:$E,$L26),"")</f>
         <v/>
       </c>
-      <c r="I26" s="18">
+      <c r="J26" s="18">
         <f>IF(AND(ISNUMBER($L26),$L26&lt;&gt;""),INDEX(Data!$F:$F,$L26),"")</f>
         <v/>
       </c>
@@ -1574,30 +1648,34 @@
         <v/>
       </c>
       <c r="C27" s="20">
+        <f>IF(AND(ISNUMBER($L27),$L27&lt;&gt;""),INDEX(Data!$J:$J,$L27),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="20">
         <f>IF(AND(ISNUMBER($L27),$L27&lt;&gt;""),INDEX(Data!$K:$K,$L27),"")</f>
         <v/>
       </c>
-      <c r="D27" s="20">
+      <c r="E27" s="20">
         <f>IF(AND(ISNUMBER($L27),$L27&lt;&gt;""),IF(INDEX(Data!$L:$L,$L27)="","—",INDEX(Data!$L:$L,$L27)),"")</f>
         <v/>
       </c>
-      <c r="E27" s="20">
+      <c r="F27" s="20">
         <f>IF(AND(ISNUMBER($L27),$L27&lt;&gt;""),IF(INDEX(Data!$M:$M,$L27)="","—",INDEX(Data!$M:$M,$L27)),"")</f>
         <v/>
       </c>
-      <c r="F27" s="21">
+      <c r="G27" s="21">
         <f>IF(AND(ISNUMBER($L27),$L27&lt;&gt;""),IF(INDEX(Data!$N:$N,$L27)="","—",INDEX(Data!$N:$N,$L27)),"")</f>
         <v/>
       </c>
-      <c r="G27" s="22">
+      <c r="H27" s="22">
         <f>IF(AND(ISNUMBER($L27),$L27&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L27)="","—",INDEX(Data!$Q:$Q,$L27)),"")</f>
         <v/>
       </c>
-      <c r="H27" s="23">
+      <c r="I27" s="23">
         <f>IF(AND(ISNUMBER($L27),$L27&lt;&gt;""),INDEX(Data!$E:$E,$L27),"")</f>
         <v/>
       </c>
-      <c r="I27" s="23">
+      <c r="J27" s="23">
         <f>IF(AND(ISNUMBER($L27),$L27&lt;&gt;""),INDEX(Data!$F:$F,$L27),"")</f>
         <v/>
       </c>
@@ -1616,30 +1694,34 @@
         <v/>
       </c>
       <c r="C28" s="15">
+        <f>IF(AND(ISNUMBER($L28),$L28&lt;&gt;""),INDEX(Data!$J:$J,$L28),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="15">
         <f>IF(AND(ISNUMBER($L28),$L28&lt;&gt;""),INDEX(Data!$K:$K,$L28),"")</f>
         <v/>
       </c>
-      <c r="D28" s="15">
+      <c r="E28" s="15">
         <f>IF(AND(ISNUMBER($L28),$L28&lt;&gt;""),IF(INDEX(Data!$L:$L,$L28)="","—",INDEX(Data!$L:$L,$L28)),"")</f>
         <v/>
       </c>
-      <c r="E28" s="15">
+      <c r="F28" s="15">
         <f>IF(AND(ISNUMBER($L28),$L28&lt;&gt;""),IF(INDEX(Data!$M:$M,$L28)="","—",INDEX(Data!$M:$M,$L28)),"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="G28" s="16">
         <f>IF(AND(ISNUMBER($L28),$L28&lt;&gt;""),IF(INDEX(Data!$N:$N,$L28)="","—",INDEX(Data!$N:$N,$L28)),"")</f>
         <v/>
       </c>
-      <c r="G28" s="17">
+      <c r="H28" s="17">
         <f>IF(AND(ISNUMBER($L28),$L28&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L28)="","—",INDEX(Data!$Q:$Q,$L28)),"")</f>
         <v/>
       </c>
-      <c r="H28" s="18">
+      <c r="I28" s="18">
         <f>IF(AND(ISNUMBER($L28),$L28&lt;&gt;""),INDEX(Data!$E:$E,$L28),"")</f>
         <v/>
       </c>
-      <c r="I28" s="18">
+      <c r="J28" s="18">
         <f>IF(AND(ISNUMBER($L28),$L28&lt;&gt;""),INDEX(Data!$F:$F,$L28),"")</f>
         <v/>
       </c>
@@ -1658,30 +1740,34 @@
         <v/>
       </c>
       <c r="C29" s="20">
+        <f>IF(AND(ISNUMBER($L29),$L29&lt;&gt;""),INDEX(Data!$J:$J,$L29),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="20">
         <f>IF(AND(ISNUMBER($L29),$L29&lt;&gt;""),INDEX(Data!$K:$K,$L29),"")</f>
         <v/>
       </c>
-      <c r="D29" s="20">
+      <c r="E29" s="20">
         <f>IF(AND(ISNUMBER($L29),$L29&lt;&gt;""),IF(INDEX(Data!$L:$L,$L29)="","—",INDEX(Data!$L:$L,$L29)),"")</f>
         <v/>
       </c>
-      <c r="E29" s="20">
+      <c r="F29" s="20">
         <f>IF(AND(ISNUMBER($L29),$L29&lt;&gt;""),IF(INDEX(Data!$M:$M,$L29)="","—",INDEX(Data!$M:$M,$L29)),"")</f>
         <v/>
       </c>
-      <c r="F29" s="21">
+      <c r="G29" s="21">
         <f>IF(AND(ISNUMBER($L29),$L29&lt;&gt;""),IF(INDEX(Data!$N:$N,$L29)="","—",INDEX(Data!$N:$N,$L29)),"")</f>
         <v/>
       </c>
-      <c r="G29" s="22">
+      <c r="H29" s="22">
         <f>IF(AND(ISNUMBER($L29),$L29&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L29)="","—",INDEX(Data!$Q:$Q,$L29)),"")</f>
         <v/>
       </c>
-      <c r="H29" s="23">
+      <c r="I29" s="23">
         <f>IF(AND(ISNUMBER($L29),$L29&lt;&gt;""),INDEX(Data!$E:$E,$L29),"")</f>
         <v/>
       </c>
-      <c r="I29" s="23">
+      <c r="J29" s="23">
         <f>IF(AND(ISNUMBER($L29),$L29&lt;&gt;""),INDEX(Data!$F:$F,$L29),"")</f>
         <v/>
       </c>
@@ -1700,30 +1786,34 @@
         <v/>
       </c>
       <c r="C30" s="15">
+        <f>IF(AND(ISNUMBER($L30),$L30&lt;&gt;""),INDEX(Data!$J:$J,$L30),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="15">
         <f>IF(AND(ISNUMBER($L30),$L30&lt;&gt;""),INDEX(Data!$K:$K,$L30),"")</f>
         <v/>
       </c>
-      <c r="D30" s="15">
+      <c r="E30" s="15">
         <f>IF(AND(ISNUMBER($L30),$L30&lt;&gt;""),IF(INDEX(Data!$L:$L,$L30)="","—",INDEX(Data!$L:$L,$L30)),"")</f>
         <v/>
       </c>
-      <c r="E30" s="15">
+      <c r="F30" s="15">
         <f>IF(AND(ISNUMBER($L30),$L30&lt;&gt;""),IF(INDEX(Data!$M:$M,$L30)="","—",INDEX(Data!$M:$M,$L30)),"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="G30" s="16">
         <f>IF(AND(ISNUMBER($L30),$L30&lt;&gt;""),IF(INDEX(Data!$N:$N,$L30)="","—",INDEX(Data!$N:$N,$L30)),"")</f>
         <v/>
       </c>
-      <c r="G30" s="17">
+      <c r="H30" s="17">
         <f>IF(AND(ISNUMBER($L30),$L30&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L30)="","—",INDEX(Data!$Q:$Q,$L30)),"")</f>
         <v/>
       </c>
-      <c r="H30" s="18">
+      <c r="I30" s="18">
         <f>IF(AND(ISNUMBER($L30),$L30&lt;&gt;""),INDEX(Data!$E:$E,$L30),"")</f>
         <v/>
       </c>
-      <c r="I30" s="18">
+      <c r="J30" s="18">
         <f>IF(AND(ISNUMBER($L30),$L30&lt;&gt;""),INDEX(Data!$F:$F,$L30),"")</f>
         <v/>
       </c>
@@ -1742,30 +1832,34 @@
         <v/>
       </c>
       <c r="C31" s="20">
+        <f>IF(AND(ISNUMBER($L31),$L31&lt;&gt;""),INDEX(Data!$J:$J,$L31),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="20">
         <f>IF(AND(ISNUMBER($L31),$L31&lt;&gt;""),INDEX(Data!$K:$K,$L31),"")</f>
         <v/>
       </c>
-      <c r="D31" s="20">
+      <c r="E31" s="20">
         <f>IF(AND(ISNUMBER($L31),$L31&lt;&gt;""),IF(INDEX(Data!$L:$L,$L31)="","—",INDEX(Data!$L:$L,$L31)),"")</f>
         <v/>
       </c>
-      <c r="E31" s="20">
+      <c r="F31" s="20">
         <f>IF(AND(ISNUMBER($L31),$L31&lt;&gt;""),IF(INDEX(Data!$M:$M,$L31)="","—",INDEX(Data!$M:$M,$L31)),"")</f>
         <v/>
       </c>
-      <c r="F31" s="21">
+      <c r="G31" s="21">
         <f>IF(AND(ISNUMBER($L31),$L31&lt;&gt;""),IF(INDEX(Data!$N:$N,$L31)="","—",INDEX(Data!$N:$N,$L31)),"")</f>
         <v/>
       </c>
-      <c r="G31" s="22">
+      <c r="H31" s="22">
         <f>IF(AND(ISNUMBER($L31),$L31&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L31)="","—",INDEX(Data!$Q:$Q,$L31)),"")</f>
         <v/>
       </c>
-      <c r="H31" s="23">
+      <c r="I31" s="23">
         <f>IF(AND(ISNUMBER($L31),$L31&lt;&gt;""),INDEX(Data!$E:$E,$L31),"")</f>
         <v/>
       </c>
-      <c r="I31" s="23">
+      <c r="J31" s="23">
         <f>IF(AND(ISNUMBER($L31),$L31&lt;&gt;""),INDEX(Data!$F:$F,$L31),"")</f>
         <v/>
       </c>
@@ -1784,30 +1878,34 @@
         <v/>
       </c>
       <c r="C32" s="15">
+        <f>IF(AND(ISNUMBER($L32),$L32&lt;&gt;""),INDEX(Data!$J:$J,$L32),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="15">
         <f>IF(AND(ISNUMBER($L32),$L32&lt;&gt;""),INDEX(Data!$K:$K,$L32),"")</f>
         <v/>
       </c>
-      <c r="D32" s="15">
+      <c r="E32" s="15">
         <f>IF(AND(ISNUMBER($L32),$L32&lt;&gt;""),IF(INDEX(Data!$L:$L,$L32)="","—",INDEX(Data!$L:$L,$L32)),"")</f>
         <v/>
       </c>
-      <c r="E32" s="15">
+      <c r="F32" s="15">
         <f>IF(AND(ISNUMBER($L32),$L32&lt;&gt;""),IF(INDEX(Data!$M:$M,$L32)="","—",INDEX(Data!$M:$M,$L32)),"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="G32" s="16">
         <f>IF(AND(ISNUMBER($L32),$L32&lt;&gt;""),IF(INDEX(Data!$N:$N,$L32)="","—",INDEX(Data!$N:$N,$L32)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="17">
+      <c r="H32" s="17">
         <f>IF(AND(ISNUMBER($L32),$L32&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L32)="","—",INDEX(Data!$Q:$Q,$L32)),"")</f>
         <v/>
       </c>
-      <c r="H32" s="18">
+      <c r="I32" s="18">
         <f>IF(AND(ISNUMBER($L32),$L32&lt;&gt;""),INDEX(Data!$E:$E,$L32),"")</f>
         <v/>
       </c>
-      <c r="I32" s="18">
+      <c r="J32" s="18">
         <f>IF(AND(ISNUMBER($L32),$L32&lt;&gt;""),INDEX(Data!$F:$F,$L32),"")</f>
         <v/>
       </c>
@@ -1826,30 +1924,34 @@
         <v/>
       </c>
       <c r="C33" s="20">
+        <f>IF(AND(ISNUMBER($L33),$L33&lt;&gt;""),INDEX(Data!$J:$J,$L33),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="20">
         <f>IF(AND(ISNUMBER($L33),$L33&lt;&gt;""),INDEX(Data!$K:$K,$L33),"")</f>
         <v/>
       </c>
-      <c r="D33" s="20">
+      <c r="E33" s="20">
         <f>IF(AND(ISNUMBER($L33),$L33&lt;&gt;""),IF(INDEX(Data!$L:$L,$L33)="","—",INDEX(Data!$L:$L,$L33)),"")</f>
         <v/>
       </c>
-      <c r="E33" s="20">
+      <c r="F33" s="20">
         <f>IF(AND(ISNUMBER($L33),$L33&lt;&gt;""),IF(INDEX(Data!$M:$M,$L33)="","—",INDEX(Data!$M:$M,$L33)),"")</f>
         <v/>
       </c>
-      <c r="F33" s="21">
+      <c r="G33" s="21">
         <f>IF(AND(ISNUMBER($L33),$L33&lt;&gt;""),IF(INDEX(Data!$N:$N,$L33)="","—",INDEX(Data!$N:$N,$L33)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="22">
+      <c r="H33" s="22">
         <f>IF(AND(ISNUMBER($L33),$L33&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L33)="","—",INDEX(Data!$Q:$Q,$L33)),"")</f>
         <v/>
       </c>
-      <c r="H33" s="23">
+      <c r="I33" s="23">
         <f>IF(AND(ISNUMBER($L33),$L33&lt;&gt;""),INDEX(Data!$E:$E,$L33),"")</f>
         <v/>
       </c>
-      <c r="I33" s="23">
+      <c r="J33" s="23">
         <f>IF(AND(ISNUMBER($L33),$L33&lt;&gt;""),INDEX(Data!$F:$F,$L33),"")</f>
         <v/>
       </c>
@@ -1868,30 +1970,34 @@
         <v/>
       </c>
       <c r="C34" s="15">
+        <f>IF(AND(ISNUMBER($L34),$L34&lt;&gt;""),INDEX(Data!$J:$J,$L34),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="15">
         <f>IF(AND(ISNUMBER($L34),$L34&lt;&gt;""),INDEX(Data!$K:$K,$L34),"")</f>
         <v/>
       </c>
-      <c r="D34" s="15">
+      <c r="E34" s="15">
         <f>IF(AND(ISNUMBER($L34),$L34&lt;&gt;""),IF(INDEX(Data!$L:$L,$L34)="","—",INDEX(Data!$L:$L,$L34)),"")</f>
         <v/>
       </c>
-      <c r="E34" s="15">
+      <c r="F34" s="15">
         <f>IF(AND(ISNUMBER($L34),$L34&lt;&gt;""),IF(INDEX(Data!$M:$M,$L34)="","—",INDEX(Data!$M:$M,$L34)),"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="G34" s="16">
         <f>IF(AND(ISNUMBER($L34),$L34&lt;&gt;""),IF(INDEX(Data!$N:$N,$L34)="","—",INDEX(Data!$N:$N,$L34)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="17">
+      <c r="H34" s="17">
         <f>IF(AND(ISNUMBER($L34),$L34&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L34)="","—",INDEX(Data!$Q:$Q,$L34)),"")</f>
         <v/>
       </c>
-      <c r="H34" s="18">
+      <c r="I34" s="18">
         <f>IF(AND(ISNUMBER($L34),$L34&lt;&gt;""),INDEX(Data!$E:$E,$L34),"")</f>
         <v/>
       </c>
-      <c r="I34" s="18">
+      <c r="J34" s="18">
         <f>IF(AND(ISNUMBER($L34),$L34&lt;&gt;""),INDEX(Data!$F:$F,$L34),"")</f>
         <v/>
       </c>
@@ -1910,30 +2016,34 @@
         <v/>
       </c>
       <c r="C35" s="20">
+        <f>IF(AND(ISNUMBER($L35),$L35&lt;&gt;""),INDEX(Data!$J:$J,$L35),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="20">
         <f>IF(AND(ISNUMBER($L35),$L35&lt;&gt;""),INDEX(Data!$K:$K,$L35),"")</f>
         <v/>
       </c>
-      <c r="D35" s="20">
+      <c r="E35" s="20">
         <f>IF(AND(ISNUMBER($L35),$L35&lt;&gt;""),IF(INDEX(Data!$L:$L,$L35)="","—",INDEX(Data!$L:$L,$L35)),"")</f>
         <v/>
       </c>
-      <c r="E35" s="20">
+      <c r="F35" s="20">
         <f>IF(AND(ISNUMBER($L35),$L35&lt;&gt;""),IF(INDEX(Data!$M:$M,$L35)="","—",INDEX(Data!$M:$M,$L35)),"")</f>
         <v/>
       </c>
-      <c r="F35" s="21">
+      <c r="G35" s="21">
         <f>IF(AND(ISNUMBER($L35),$L35&lt;&gt;""),IF(INDEX(Data!$N:$N,$L35)="","—",INDEX(Data!$N:$N,$L35)),"")</f>
         <v/>
       </c>
-      <c r="G35" s="22">
+      <c r="H35" s="22">
         <f>IF(AND(ISNUMBER($L35),$L35&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L35)="","—",INDEX(Data!$Q:$Q,$L35)),"")</f>
         <v/>
       </c>
-      <c r="H35" s="23">
+      <c r="I35" s="23">
         <f>IF(AND(ISNUMBER($L35),$L35&lt;&gt;""),INDEX(Data!$E:$E,$L35),"")</f>
         <v/>
       </c>
-      <c r="I35" s="23">
+      <c r="J35" s="23">
         <f>IF(AND(ISNUMBER($L35),$L35&lt;&gt;""),INDEX(Data!$F:$F,$L35),"")</f>
         <v/>
       </c>
@@ -1952,30 +2062,34 @@
         <v/>
       </c>
       <c r="C36" s="15">
+        <f>IF(AND(ISNUMBER($L36),$L36&lt;&gt;""),INDEX(Data!$J:$J,$L36),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="15">
         <f>IF(AND(ISNUMBER($L36),$L36&lt;&gt;""),INDEX(Data!$K:$K,$L36),"")</f>
         <v/>
       </c>
-      <c r="D36" s="15">
+      <c r="E36" s="15">
         <f>IF(AND(ISNUMBER($L36),$L36&lt;&gt;""),IF(INDEX(Data!$L:$L,$L36)="","—",INDEX(Data!$L:$L,$L36)),"")</f>
         <v/>
       </c>
-      <c r="E36" s="15">
+      <c r="F36" s="15">
         <f>IF(AND(ISNUMBER($L36),$L36&lt;&gt;""),IF(INDEX(Data!$M:$M,$L36)="","—",INDEX(Data!$M:$M,$L36)),"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="G36" s="16">
         <f>IF(AND(ISNUMBER($L36),$L36&lt;&gt;""),IF(INDEX(Data!$N:$N,$L36)="","—",INDEX(Data!$N:$N,$L36)),"")</f>
         <v/>
       </c>
-      <c r="G36" s="17">
+      <c r="H36" s="17">
         <f>IF(AND(ISNUMBER($L36),$L36&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L36)="","—",INDEX(Data!$Q:$Q,$L36)),"")</f>
         <v/>
       </c>
-      <c r="H36" s="18">
+      <c r="I36" s="18">
         <f>IF(AND(ISNUMBER($L36),$L36&lt;&gt;""),INDEX(Data!$E:$E,$L36),"")</f>
         <v/>
       </c>
-      <c r="I36" s="18">
+      <c r="J36" s="18">
         <f>IF(AND(ISNUMBER($L36),$L36&lt;&gt;""),INDEX(Data!$F:$F,$L36),"")</f>
         <v/>
       </c>
@@ -1994,30 +2108,34 @@
         <v/>
       </c>
       <c r="C37" s="20">
+        <f>IF(AND(ISNUMBER($L37),$L37&lt;&gt;""),INDEX(Data!$J:$J,$L37),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="20">
         <f>IF(AND(ISNUMBER($L37),$L37&lt;&gt;""),INDEX(Data!$K:$K,$L37),"")</f>
         <v/>
       </c>
-      <c r="D37" s="20">
+      <c r="E37" s="20">
         <f>IF(AND(ISNUMBER($L37),$L37&lt;&gt;""),IF(INDEX(Data!$L:$L,$L37)="","—",INDEX(Data!$L:$L,$L37)),"")</f>
         <v/>
       </c>
-      <c r="E37" s="20">
+      <c r="F37" s="20">
         <f>IF(AND(ISNUMBER($L37),$L37&lt;&gt;""),IF(INDEX(Data!$M:$M,$L37)="","—",INDEX(Data!$M:$M,$L37)),"")</f>
         <v/>
       </c>
-      <c r="F37" s="21">
+      <c r="G37" s="21">
         <f>IF(AND(ISNUMBER($L37),$L37&lt;&gt;""),IF(INDEX(Data!$N:$N,$L37)="","—",INDEX(Data!$N:$N,$L37)),"")</f>
         <v/>
       </c>
-      <c r="G37" s="22">
+      <c r="H37" s="22">
         <f>IF(AND(ISNUMBER($L37),$L37&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L37)="","—",INDEX(Data!$Q:$Q,$L37)),"")</f>
         <v/>
       </c>
-      <c r="H37" s="23">
+      <c r="I37" s="23">
         <f>IF(AND(ISNUMBER($L37),$L37&lt;&gt;""),INDEX(Data!$E:$E,$L37),"")</f>
         <v/>
       </c>
-      <c r="I37" s="23">
+      <c r="J37" s="23">
         <f>IF(AND(ISNUMBER($L37),$L37&lt;&gt;""),INDEX(Data!$F:$F,$L37),"")</f>
         <v/>
       </c>
@@ -2036,30 +2154,34 @@
         <v/>
       </c>
       <c r="C38" s="15">
+        <f>IF(AND(ISNUMBER($L38),$L38&lt;&gt;""),INDEX(Data!$J:$J,$L38),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="15">
         <f>IF(AND(ISNUMBER($L38),$L38&lt;&gt;""),INDEX(Data!$K:$K,$L38),"")</f>
         <v/>
       </c>
-      <c r="D38" s="15">
+      <c r="E38" s="15">
         <f>IF(AND(ISNUMBER($L38),$L38&lt;&gt;""),IF(INDEX(Data!$L:$L,$L38)="","—",INDEX(Data!$L:$L,$L38)),"")</f>
         <v/>
       </c>
-      <c r="E38" s="15">
+      <c r="F38" s="15">
         <f>IF(AND(ISNUMBER($L38),$L38&lt;&gt;""),IF(INDEX(Data!$M:$M,$L38)="","—",INDEX(Data!$M:$M,$L38)),"")</f>
         <v/>
       </c>
-      <c r="F38" s="16">
+      <c r="G38" s="16">
         <f>IF(AND(ISNUMBER($L38),$L38&lt;&gt;""),IF(INDEX(Data!$N:$N,$L38)="","—",INDEX(Data!$N:$N,$L38)),"")</f>
         <v/>
       </c>
-      <c r="G38" s="17">
+      <c r="H38" s="17">
         <f>IF(AND(ISNUMBER($L38),$L38&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L38)="","—",INDEX(Data!$Q:$Q,$L38)),"")</f>
         <v/>
       </c>
-      <c r="H38" s="18">
+      <c r="I38" s="18">
         <f>IF(AND(ISNUMBER($L38),$L38&lt;&gt;""),INDEX(Data!$E:$E,$L38),"")</f>
         <v/>
       </c>
-      <c r="I38" s="18">
+      <c r="J38" s="18">
         <f>IF(AND(ISNUMBER($L38),$L38&lt;&gt;""),INDEX(Data!$F:$F,$L38),"")</f>
         <v/>
       </c>
@@ -2078,30 +2200,34 @@
         <v/>
       </c>
       <c r="C39" s="20">
+        <f>IF(AND(ISNUMBER($L39),$L39&lt;&gt;""),INDEX(Data!$J:$J,$L39),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="20">
         <f>IF(AND(ISNUMBER($L39),$L39&lt;&gt;""),INDEX(Data!$K:$K,$L39),"")</f>
         <v/>
       </c>
-      <c r="D39" s="20">
+      <c r="E39" s="20">
         <f>IF(AND(ISNUMBER($L39),$L39&lt;&gt;""),IF(INDEX(Data!$L:$L,$L39)="","—",INDEX(Data!$L:$L,$L39)),"")</f>
         <v/>
       </c>
-      <c r="E39" s="20">
+      <c r="F39" s="20">
         <f>IF(AND(ISNUMBER($L39),$L39&lt;&gt;""),IF(INDEX(Data!$M:$M,$L39)="","—",INDEX(Data!$M:$M,$L39)),"")</f>
         <v/>
       </c>
-      <c r="F39" s="21">
+      <c r="G39" s="21">
         <f>IF(AND(ISNUMBER($L39),$L39&lt;&gt;""),IF(INDEX(Data!$N:$N,$L39)="","—",INDEX(Data!$N:$N,$L39)),"")</f>
         <v/>
       </c>
-      <c r="G39" s="22">
+      <c r="H39" s="22">
         <f>IF(AND(ISNUMBER($L39),$L39&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L39)="","—",INDEX(Data!$Q:$Q,$L39)),"")</f>
         <v/>
       </c>
-      <c r="H39" s="23">
+      <c r="I39" s="23">
         <f>IF(AND(ISNUMBER($L39),$L39&lt;&gt;""),INDEX(Data!$E:$E,$L39),"")</f>
         <v/>
       </c>
-      <c r="I39" s="23">
+      <c r="J39" s="23">
         <f>IF(AND(ISNUMBER($L39),$L39&lt;&gt;""),INDEX(Data!$F:$F,$L39),"")</f>
         <v/>
       </c>
@@ -2120,30 +2246,34 @@
         <v/>
       </c>
       <c r="C40" s="15">
+        <f>IF(AND(ISNUMBER($L40),$L40&lt;&gt;""),INDEX(Data!$J:$J,$L40),"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="15">
         <f>IF(AND(ISNUMBER($L40),$L40&lt;&gt;""),INDEX(Data!$K:$K,$L40),"")</f>
         <v/>
       </c>
-      <c r="D40" s="15">
+      <c r="E40" s="15">
         <f>IF(AND(ISNUMBER($L40),$L40&lt;&gt;""),IF(INDEX(Data!$L:$L,$L40)="","—",INDEX(Data!$L:$L,$L40)),"")</f>
         <v/>
       </c>
-      <c r="E40" s="15">
+      <c r="F40" s="15">
         <f>IF(AND(ISNUMBER($L40),$L40&lt;&gt;""),IF(INDEX(Data!$M:$M,$L40)="","—",INDEX(Data!$M:$M,$L40)),"")</f>
         <v/>
       </c>
-      <c r="F40" s="16">
+      <c r="G40" s="16">
         <f>IF(AND(ISNUMBER($L40),$L40&lt;&gt;""),IF(INDEX(Data!$N:$N,$L40)="","—",INDEX(Data!$N:$N,$L40)),"")</f>
         <v/>
       </c>
-      <c r="G40" s="17">
+      <c r="H40" s="17">
         <f>IF(AND(ISNUMBER($L40),$L40&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L40)="","—",INDEX(Data!$Q:$Q,$L40)),"")</f>
         <v/>
       </c>
-      <c r="H40" s="18">
+      <c r="I40" s="18">
         <f>IF(AND(ISNUMBER($L40),$L40&lt;&gt;""),INDEX(Data!$E:$E,$L40),"")</f>
         <v/>
       </c>
-      <c r="I40" s="18">
+      <c r="J40" s="18">
         <f>IF(AND(ISNUMBER($L40),$L40&lt;&gt;""),INDEX(Data!$F:$F,$L40),"")</f>
         <v/>
       </c>
@@ -2162,30 +2292,34 @@
         <v/>
       </c>
       <c r="C41" s="20">
+        <f>IF(AND(ISNUMBER($L41),$L41&lt;&gt;""),INDEX(Data!$J:$J,$L41),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="20">
         <f>IF(AND(ISNUMBER($L41),$L41&lt;&gt;""),INDEX(Data!$K:$K,$L41),"")</f>
         <v/>
       </c>
-      <c r="D41" s="20">
+      <c r="E41" s="20">
         <f>IF(AND(ISNUMBER($L41),$L41&lt;&gt;""),IF(INDEX(Data!$L:$L,$L41)="","—",INDEX(Data!$L:$L,$L41)),"")</f>
         <v/>
       </c>
-      <c r="E41" s="20">
+      <c r="F41" s="20">
         <f>IF(AND(ISNUMBER($L41),$L41&lt;&gt;""),IF(INDEX(Data!$M:$M,$L41)="","—",INDEX(Data!$M:$M,$L41)),"")</f>
         <v/>
       </c>
-      <c r="F41" s="21">
+      <c r="G41" s="21">
         <f>IF(AND(ISNUMBER($L41),$L41&lt;&gt;""),IF(INDEX(Data!$N:$N,$L41)="","—",INDEX(Data!$N:$N,$L41)),"")</f>
         <v/>
       </c>
-      <c r="G41" s="22">
+      <c r="H41" s="22">
         <f>IF(AND(ISNUMBER($L41),$L41&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L41)="","—",INDEX(Data!$Q:$Q,$L41)),"")</f>
         <v/>
       </c>
-      <c r="H41" s="23">
+      <c r="I41" s="23">
         <f>IF(AND(ISNUMBER($L41),$L41&lt;&gt;""),INDEX(Data!$E:$E,$L41),"")</f>
         <v/>
       </c>
-      <c r="I41" s="23">
+      <c r="J41" s="23">
         <f>IF(AND(ISNUMBER($L41),$L41&lt;&gt;""),INDEX(Data!$F:$F,$L41),"")</f>
         <v/>
       </c>
@@ -2204,30 +2338,34 @@
         <v/>
       </c>
       <c r="C42" s="15">
+        <f>IF(AND(ISNUMBER($L42),$L42&lt;&gt;""),INDEX(Data!$J:$J,$L42),"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="15">
         <f>IF(AND(ISNUMBER($L42),$L42&lt;&gt;""),INDEX(Data!$K:$K,$L42),"")</f>
         <v/>
       </c>
-      <c r="D42" s="15">
+      <c r="E42" s="15">
         <f>IF(AND(ISNUMBER($L42),$L42&lt;&gt;""),IF(INDEX(Data!$L:$L,$L42)="","—",INDEX(Data!$L:$L,$L42)),"")</f>
         <v/>
       </c>
-      <c r="E42" s="15">
+      <c r="F42" s="15">
         <f>IF(AND(ISNUMBER($L42),$L42&lt;&gt;""),IF(INDEX(Data!$M:$M,$L42)="","—",INDEX(Data!$M:$M,$L42)),"")</f>
         <v/>
       </c>
-      <c r="F42" s="16">
+      <c r="G42" s="16">
         <f>IF(AND(ISNUMBER($L42),$L42&lt;&gt;""),IF(INDEX(Data!$N:$N,$L42)="","—",INDEX(Data!$N:$N,$L42)),"")</f>
         <v/>
       </c>
-      <c r="G42" s="17">
+      <c r="H42" s="17">
         <f>IF(AND(ISNUMBER($L42),$L42&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L42)="","—",INDEX(Data!$Q:$Q,$L42)),"")</f>
         <v/>
       </c>
-      <c r="H42" s="18">
+      <c r="I42" s="18">
         <f>IF(AND(ISNUMBER($L42),$L42&lt;&gt;""),INDEX(Data!$E:$E,$L42),"")</f>
         <v/>
       </c>
-      <c r="I42" s="18">
+      <c r="J42" s="18">
         <f>IF(AND(ISNUMBER($L42),$L42&lt;&gt;""),INDEX(Data!$F:$F,$L42),"")</f>
         <v/>
       </c>
@@ -2246,30 +2384,34 @@
         <v/>
       </c>
       <c r="C43" s="20">
+        <f>IF(AND(ISNUMBER($L43),$L43&lt;&gt;""),INDEX(Data!$J:$J,$L43),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="20">
         <f>IF(AND(ISNUMBER($L43),$L43&lt;&gt;""),INDEX(Data!$K:$K,$L43),"")</f>
         <v/>
       </c>
-      <c r="D43" s="20">
+      <c r="E43" s="20">
         <f>IF(AND(ISNUMBER($L43),$L43&lt;&gt;""),IF(INDEX(Data!$L:$L,$L43)="","—",INDEX(Data!$L:$L,$L43)),"")</f>
         <v/>
       </c>
-      <c r="E43" s="20">
+      <c r="F43" s="20">
         <f>IF(AND(ISNUMBER($L43),$L43&lt;&gt;""),IF(INDEX(Data!$M:$M,$L43)="","—",INDEX(Data!$M:$M,$L43)),"")</f>
         <v/>
       </c>
-      <c r="F43" s="21">
+      <c r="G43" s="21">
         <f>IF(AND(ISNUMBER($L43),$L43&lt;&gt;""),IF(INDEX(Data!$N:$N,$L43)="","—",INDEX(Data!$N:$N,$L43)),"")</f>
         <v/>
       </c>
-      <c r="G43" s="22">
+      <c r="H43" s="22">
         <f>IF(AND(ISNUMBER($L43),$L43&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L43)="","—",INDEX(Data!$Q:$Q,$L43)),"")</f>
         <v/>
       </c>
-      <c r="H43" s="23">
+      <c r="I43" s="23">
         <f>IF(AND(ISNUMBER($L43),$L43&lt;&gt;""),INDEX(Data!$E:$E,$L43),"")</f>
         <v/>
       </c>
-      <c r="I43" s="23">
+      <c r="J43" s="23">
         <f>IF(AND(ISNUMBER($L43),$L43&lt;&gt;""),INDEX(Data!$F:$F,$L43),"")</f>
         <v/>
       </c>
@@ -2288,30 +2430,34 @@
         <v/>
       </c>
       <c r="C44" s="15">
+        <f>IF(AND(ISNUMBER($L44),$L44&lt;&gt;""),INDEX(Data!$J:$J,$L44),"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="15">
         <f>IF(AND(ISNUMBER($L44),$L44&lt;&gt;""),INDEX(Data!$K:$K,$L44),"")</f>
         <v/>
       </c>
-      <c r="D44" s="15">
+      <c r="E44" s="15">
         <f>IF(AND(ISNUMBER($L44),$L44&lt;&gt;""),IF(INDEX(Data!$L:$L,$L44)="","—",INDEX(Data!$L:$L,$L44)),"")</f>
         <v/>
       </c>
-      <c r="E44" s="15">
+      <c r="F44" s="15">
         <f>IF(AND(ISNUMBER($L44),$L44&lt;&gt;""),IF(INDEX(Data!$M:$M,$L44)="","—",INDEX(Data!$M:$M,$L44)),"")</f>
         <v/>
       </c>
-      <c r="F44" s="16">
+      <c r="G44" s="16">
         <f>IF(AND(ISNUMBER($L44),$L44&lt;&gt;""),IF(INDEX(Data!$N:$N,$L44)="","—",INDEX(Data!$N:$N,$L44)),"")</f>
         <v/>
       </c>
-      <c r="G44" s="17">
+      <c r="H44" s="17">
         <f>IF(AND(ISNUMBER($L44),$L44&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L44)="","—",INDEX(Data!$Q:$Q,$L44)),"")</f>
         <v/>
       </c>
-      <c r="H44" s="18">
+      <c r="I44" s="18">
         <f>IF(AND(ISNUMBER($L44),$L44&lt;&gt;""),INDEX(Data!$E:$E,$L44),"")</f>
         <v/>
       </c>
-      <c r="I44" s="18">
+      <c r="J44" s="18">
         <f>IF(AND(ISNUMBER($L44),$L44&lt;&gt;""),INDEX(Data!$F:$F,$L44),"")</f>
         <v/>
       </c>
@@ -2330,30 +2476,34 @@
         <v/>
       </c>
       <c r="C45" s="20">
+        <f>IF(AND(ISNUMBER($L45),$L45&lt;&gt;""),INDEX(Data!$J:$J,$L45),"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="20">
         <f>IF(AND(ISNUMBER($L45),$L45&lt;&gt;""),INDEX(Data!$K:$K,$L45),"")</f>
         <v/>
       </c>
-      <c r="D45" s="20">
+      <c r="E45" s="20">
         <f>IF(AND(ISNUMBER($L45),$L45&lt;&gt;""),IF(INDEX(Data!$L:$L,$L45)="","—",INDEX(Data!$L:$L,$L45)),"")</f>
         <v/>
       </c>
-      <c r="E45" s="20">
+      <c r="F45" s="20">
         <f>IF(AND(ISNUMBER($L45),$L45&lt;&gt;""),IF(INDEX(Data!$M:$M,$L45)="","—",INDEX(Data!$M:$M,$L45)),"")</f>
         <v/>
       </c>
-      <c r="F45" s="21">
+      <c r="G45" s="21">
         <f>IF(AND(ISNUMBER($L45),$L45&lt;&gt;""),IF(INDEX(Data!$N:$N,$L45)="","—",INDEX(Data!$N:$N,$L45)),"")</f>
         <v/>
       </c>
-      <c r="G45" s="22">
+      <c r="H45" s="22">
         <f>IF(AND(ISNUMBER($L45),$L45&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L45)="","—",INDEX(Data!$Q:$Q,$L45)),"")</f>
         <v/>
       </c>
-      <c r="H45" s="23">
+      <c r="I45" s="23">
         <f>IF(AND(ISNUMBER($L45),$L45&lt;&gt;""),INDEX(Data!$E:$E,$L45),"")</f>
         <v/>
       </c>
-      <c r="I45" s="23">
+      <c r="J45" s="23">
         <f>IF(AND(ISNUMBER($L45),$L45&lt;&gt;""),INDEX(Data!$F:$F,$L45),"")</f>
         <v/>
       </c>
@@ -2372,30 +2522,34 @@
         <v/>
       </c>
       <c r="C46" s="15">
+        <f>IF(AND(ISNUMBER($L46),$L46&lt;&gt;""),INDEX(Data!$J:$J,$L46),"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="15">
         <f>IF(AND(ISNUMBER($L46),$L46&lt;&gt;""),INDEX(Data!$K:$K,$L46),"")</f>
         <v/>
       </c>
-      <c r="D46" s="15">
+      <c r="E46" s="15">
         <f>IF(AND(ISNUMBER($L46),$L46&lt;&gt;""),IF(INDEX(Data!$L:$L,$L46)="","—",INDEX(Data!$L:$L,$L46)),"")</f>
         <v/>
       </c>
-      <c r="E46" s="15">
+      <c r="F46" s="15">
         <f>IF(AND(ISNUMBER($L46),$L46&lt;&gt;""),IF(INDEX(Data!$M:$M,$L46)="","—",INDEX(Data!$M:$M,$L46)),"")</f>
         <v/>
       </c>
-      <c r="F46" s="16">
+      <c r="G46" s="16">
         <f>IF(AND(ISNUMBER($L46),$L46&lt;&gt;""),IF(INDEX(Data!$N:$N,$L46)="","—",INDEX(Data!$N:$N,$L46)),"")</f>
         <v/>
       </c>
-      <c r="G46" s="17">
+      <c r="H46" s="17">
         <f>IF(AND(ISNUMBER($L46),$L46&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L46)="","—",INDEX(Data!$Q:$Q,$L46)),"")</f>
         <v/>
       </c>
-      <c r="H46" s="18">
+      <c r="I46" s="18">
         <f>IF(AND(ISNUMBER($L46),$L46&lt;&gt;""),INDEX(Data!$E:$E,$L46),"")</f>
         <v/>
       </c>
-      <c r="I46" s="18">
+      <c r="J46" s="18">
         <f>IF(AND(ISNUMBER($L46),$L46&lt;&gt;""),INDEX(Data!$F:$F,$L46),"")</f>
         <v/>
       </c>
@@ -2414,30 +2568,34 @@
         <v/>
       </c>
       <c r="C47" s="20">
+        <f>IF(AND(ISNUMBER($L47),$L47&lt;&gt;""),INDEX(Data!$J:$J,$L47),"")</f>
+        <v/>
+      </c>
+      <c r="D47" s="20">
         <f>IF(AND(ISNUMBER($L47),$L47&lt;&gt;""),INDEX(Data!$K:$K,$L47),"")</f>
         <v/>
       </c>
-      <c r="D47" s="20">
+      <c r="E47" s="20">
         <f>IF(AND(ISNUMBER($L47),$L47&lt;&gt;""),IF(INDEX(Data!$L:$L,$L47)="","—",INDEX(Data!$L:$L,$L47)),"")</f>
         <v/>
       </c>
-      <c r="E47" s="20">
+      <c r="F47" s="20">
         <f>IF(AND(ISNUMBER($L47),$L47&lt;&gt;""),IF(INDEX(Data!$M:$M,$L47)="","—",INDEX(Data!$M:$M,$L47)),"")</f>
         <v/>
       </c>
-      <c r="F47" s="21">
+      <c r="G47" s="21">
         <f>IF(AND(ISNUMBER($L47),$L47&lt;&gt;""),IF(INDEX(Data!$N:$N,$L47)="","—",INDEX(Data!$N:$N,$L47)),"")</f>
         <v/>
       </c>
-      <c r="G47" s="22">
+      <c r="H47" s="22">
         <f>IF(AND(ISNUMBER($L47),$L47&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L47)="","—",INDEX(Data!$Q:$Q,$L47)),"")</f>
         <v/>
       </c>
-      <c r="H47" s="23">
+      <c r="I47" s="23">
         <f>IF(AND(ISNUMBER($L47),$L47&lt;&gt;""),INDEX(Data!$E:$E,$L47),"")</f>
         <v/>
       </c>
-      <c r="I47" s="23">
+      <c r="J47" s="23">
         <f>IF(AND(ISNUMBER($L47),$L47&lt;&gt;""),INDEX(Data!$F:$F,$L47),"")</f>
         <v/>
       </c>
@@ -2456,30 +2614,34 @@
         <v/>
       </c>
       <c r="C48" s="15">
+        <f>IF(AND(ISNUMBER($L48),$L48&lt;&gt;""),INDEX(Data!$J:$J,$L48),"")</f>
+        <v/>
+      </c>
+      <c r="D48" s="15">
         <f>IF(AND(ISNUMBER($L48),$L48&lt;&gt;""),INDEX(Data!$K:$K,$L48),"")</f>
         <v/>
       </c>
-      <c r="D48" s="15">
+      <c r="E48" s="15">
         <f>IF(AND(ISNUMBER($L48),$L48&lt;&gt;""),IF(INDEX(Data!$L:$L,$L48)="","—",INDEX(Data!$L:$L,$L48)),"")</f>
         <v/>
       </c>
-      <c r="E48" s="15">
+      <c r="F48" s="15">
         <f>IF(AND(ISNUMBER($L48),$L48&lt;&gt;""),IF(INDEX(Data!$M:$M,$L48)="","—",INDEX(Data!$M:$M,$L48)),"")</f>
         <v/>
       </c>
-      <c r="F48" s="16">
+      <c r="G48" s="16">
         <f>IF(AND(ISNUMBER($L48),$L48&lt;&gt;""),IF(INDEX(Data!$N:$N,$L48)="","—",INDEX(Data!$N:$N,$L48)),"")</f>
         <v/>
       </c>
-      <c r="G48" s="17">
+      <c r="H48" s="17">
         <f>IF(AND(ISNUMBER($L48),$L48&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L48)="","—",INDEX(Data!$Q:$Q,$L48)),"")</f>
         <v/>
       </c>
-      <c r="H48" s="18">
+      <c r="I48" s="18">
         <f>IF(AND(ISNUMBER($L48),$L48&lt;&gt;""),INDEX(Data!$E:$E,$L48),"")</f>
         <v/>
       </c>
-      <c r="I48" s="18">
+      <c r="J48" s="18">
         <f>IF(AND(ISNUMBER($L48),$L48&lt;&gt;""),INDEX(Data!$F:$F,$L48),"")</f>
         <v/>
       </c>
@@ -2498,30 +2660,34 @@
         <v/>
       </c>
       <c r="C49" s="20">
+        <f>IF(AND(ISNUMBER($L49),$L49&lt;&gt;""),INDEX(Data!$J:$J,$L49),"")</f>
+        <v/>
+      </c>
+      <c r="D49" s="20">
         <f>IF(AND(ISNUMBER($L49),$L49&lt;&gt;""),INDEX(Data!$K:$K,$L49),"")</f>
         <v/>
       </c>
-      <c r="D49" s="20">
+      <c r="E49" s="20">
         <f>IF(AND(ISNUMBER($L49),$L49&lt;&gt;""),IF(INDEX(Data!$L:$L,$L49)="","—",INDEX(Data!$L:$L,$L49)),"")</f>
         <v/>
       </c>
-      <c r="E49" s="20">
+      <c r="F49" s="20">
         <f>IF(AND(ISNUMBER($L49),$L49&lt;&gt;""),IF(INDEX(Data!$M:$M,$L49)="","—",INDEX(Data!$M:$M,$L49)),"")</f>
         <v/>
       </c>
-      <c r="F49" s="21">
+      <c r="G49" s="21">
         <f>IF(AND(ISNUMBER($L49),$L49&lt;&gt;""),IF(INDEX(Data!$N:$N,$L49)="","—",INDEX(Data!$N:$N,$L49)),"")</f>
         <v/>
       </c>
-      <c r="G49" s="22">
+      <c r="H49" s="22">
         <f>IF(AND(ISNUMBER($L49),$L49&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L49)="","—",INDEX(Data!$Q:$Q,$L49)),"")</f>
         <v/>
       </c>
-      <c r="H49" s="23">
+      <c r="I49" s="23">
         <f>IF(AND(ISNUMBER($L49),$L49&lt;&gt;""),INDEX(Data!$E:$E,$L49),"")</f>
         <v/>
       </c>
-      <c r="I49" s="23">
+      <c r="J49" s="23">
         <f>IF(AND(ISNUMBER($L49),$L49&lt;&gt;""),INDEX(Data!$F:$F,$L49),"")</f>
         <v/>
       </c>
@@ -2540,30 +2706,34 @@
         <v/>
       </c>
       <c r="C50" s="15">
+        <f>IF(AND(ISNUMBER($L50),$L50&lt;&gt;""),INDEX(Data!$J:$J,$L50),"")</f>
+        <v/>
+      </c>
+      <c r="D50" s="15">
         <f>IF(AND(ISNUMBER($L50),$L50&lt;&gt;""),INDEX(Data!$K:$K,$L50),"")</f>
         <v/>
       </c>
-      <c r="D50" s="15">
+      <c r="E50" s="15">
         <f>IF(AND(ISNUMBER($L50),$L50&lt;&gt;""),IF(INDEX(Data!$L:$L,$L50)="","—",INDEX(Data!$L:$L,$L50)),"")</f>
         <v/>
       </c>
-      <c r="E50" s="15">
+      <c r="F50" s="15">
         <f>IF(AND(ISNUMBER($L50),$L50&lt;&gt;""),IF(INDEX(Data!$M:$M,$L50)="","—",INDEX(Data!$M:$M,$L50)),"")</f>
         <v/>
       </c>
-      <c r="F50" s="16">
+      <c r="G50" s="16">
         <f>IF(AND(ISNUMBER($L50),$L50&lt;&gt;""),IF(INDEX(Data!$N:$N,$L50)="","—",INDEX(Data!$N:$N,$L50)),"")</f>
         <v/>
       </c>
-      <c r="G50" s="17">
+      <c r="H50" s="17">
         <f>IF(AND(ISNUMBER($L50),$L50&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L50)="","—",INDEX(Data!$Q:$Q,$L50)),"")</f>
         <v/>
       </c>
-      <c r="H50" s="18">
+      <c r="I50" s="18">
         <f>IF(AND(ISNUMBER($L50),$L50&lt;&gt;""),INDEX(Data!$E:$E,$L50),"")</f>
         <v/>
       </c>
-      <c r="I50" s="18">
+      <c r="J50" s="18">
         <f>IF(AND(ISNUMBER($L50),$L50&lt;&gt;""),INDEX(Data!$F:$F,$L50),"")</f>
         <v/>
       </c>
@@ -2582,30 +2752,34 @@
         <v/>
       </c>
       <c r="C51" s="20">
+        <f>IF(AND(ISNUMBER($L51),$L51&lt;&gt;""),INDEX(Data!$J:$J,$L51),"")</f>
+        <v/>
+      </c>
+      <c r="D51" s="20">
         <f>IF(AND(ISNUMBER($L51),$L51&lt;&gt;""),INDEX(Data!$K:$K,$L51),"")</f>
         <v/>
       </c>
-      <c r="D51" s="20">
+      <c r="E51" s="20">
         <f>IF(AND(ISNUMBER($L51),$L51&lt;&gt;""),IF(INDEX(Data!$L:$L,$L51)="","—",INDEX(Data!$L:$L,$L51)),"")</f>
         <v/>
       </c>
-      <c r="E51" s="20">
+      <c r="F51" s="20">
         <f>IF(AND(ISNUMBER($L51),$L51&lt;&gt;""),IF(INDEX(Data!$M:$M,$L51)="","—",INDEX(Data!$M:$M,$L51)),"")</f>
         <v/>
       </c>
-      <c r="F51" s="21">
+      <c r="G51" s="21">
         <f>IF(AND(ISNUMBER($L51),$L51&lt;&gt;""),IF(INDEX(Data!$N:$N,$L51)="","—",INDEX(Data!$N:$N,$L51)),"")</f>
         <v/>
       </c>
-      <c r="G51" s="22">
+      <c r="H51" s="22">
         <f>IF(AND(ISNUMBER($L51),$L51&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L51)="","—",INDEX(Data!$Q:$Q,$L51)),"")</f>
         <v/>
       </c>
-      <c r="H51" s="23">
+      <c r="I51" s="23">
         <f>IF(AND(ISNUMBER($L51),$L51&lt;&gt;""),INDEX(Data!$E:$E,$L51),"")</f>
         <v/>
       </c>
-      <c r="I51" s="23">
+      <c r="J51" s="23">
         <f>IF(AND(ISNUMBER($L51),$L51&lt;&gt;""),INDEX(Data!$F:$F,$L51),"")</f>
         <v/>
       </c>
@@ -2624,30 +2798,34 @@
         <v/>
       </c>
       <c r="C52" s="15">
+        <f>IF(AND(ISNUMBER($L52),$L52&lt;&gt;""),INDEX(Data!$J:$J,$L52),"")</f>
+        <v/>
+      </c>
+      <c r="D52" s="15">
         <f>IF(AND(ISNUMBER($L52),$L52&lt;&gt;""),INDEX(Data!$K:$K,$L52),"")</f>
         <v/>
       </c>
-      <c r="D52" s="15">
+      <c r="E52" s="15">
         <f>IF(AND(ISNUMBER($L52),$L52&lt;&gt;""),IF(INDEX(Data!$L:$L,$L52)="","—",INDEX(Data!$L:$L,$L52)),"")</f>
         <v/>
       </c>
-      <c r="E52" s="15">
+      <c r="F52" s="15">
         <f>IF(AND(ISNUMBER($L52),$L52&lt;&gt;""),IF(INDEX(Data!$M:$M,$L52)="","—",INDEX(Data!$M:$M,$L52)),"")</f>
         <v/>
       </c>
-      <c r="F52" s="16">
+      <c r="G52" s="16">
         <f>IF(AND(ISNUMBER($L52),$L52&lt;&gt;""),IF(INDEX(Data!$N:$N,$L52)="","—",INDEX(Data!$N:$N,$L52)),"")</f>
         <v/>
       </c>
-      <c r="G52" s="17">
+      <c r="H52" s="17">
         <f>IF(AND(ISNUMBER($L52),$L52&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L52)="","—",INDEX(Data!$Q:$Q,$L52)),"")</f>
         <v/>
       </c>
-      <c r="H52" s="18">
+      <c r="I52" s="18">
         <f>IF(AND(ISNUMBER($L52),$L52&lt;&gt;""),INDEX(Data!$E:$E,$L52),"")</f>
         <v/>
       </c>
-      <c r="I52" s="18">
+      <c r="J52" s="18">
         <f>IF(AND(ISNUMBER($L52),$L52&lt;&gt;""),INDEX(Data!$F:$F,$L52),"")</f>
         <v/>
       </c>
@@ -2666,30 +2844,34 @@
         <v/>
       </c>
       <c r="C53" s="20">
+        <f>IF(AND(ISNUMBER($L53),$L53&lt;&gt;""),INDEX(Data!$J:$J,$L53),"")</f>
+        <v/>
+      </c>
+      <c r="D53" s="20">
         <f>IF(AND(ISNUMBER($L53),$L53&lt;&gt;""),INDEX(Data!$K:$K,$L53),"")</f>
         <v/>
       </c>
-      <c r="D53" s="20">
+      <c r="E53" s="20">
         <f>IF(AND(ISNUMBER($L53),$L53&lt;&gt;""),IF(INDEX(Data!$L:$L,$L53)="","—",INDEX(Data!$L:$L,$L53)),"")</f>
         <v/>
       </c>
-      <c r="E53" s="20">
+      <c r="F53" s="20">
         <f>IF(AND(ISNUMBER($L53),$L53&lt;&gt;""),IF(INDEX(Data!$M:$M,$L53)="","—",INDEX(Data!$M:$M,$L53)),"")</f>
         <v/>
       </c>
-      <c r="F53" s="21">
+      <c r="G53" s="21">
         <f>IF(AND(ISNUMBER($L53),$L53&lt;&gt;""),IF(INDEX(Data!$N:$N,$L53)="","—",INDEX(Data!$N:$N,$L53)),"")</f>
         <v/>
       </c>
-      <c r="G53" s="22">
+      <c r="H53" s="22">
         <f>IF(AND(ISNUMBER($L53),$L53&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L53)="","—",INDEX(Data!$Q:$Q,$L53)),"")</f>
         <v/>
       </c>
-      <c r="H53" s="23">
+      <c r="I53" s="23">
         <f>IF(AND(ISNUMBER($L53),$L53&lt;&gt;""),INDEX(Data!$E:$E,$L53),"")</f>
         <v/>
       </c>
-      <c r="I53" s="23">
+      <c r="J53" s="23">
         <f>IF(AND(ISNUMBER($L53),$L53&lt;&gt;""),INDEX(Data!$F:$F,$L53),"")</f>
         <v/>
       </c>
@@ -2708,30 +2890,34 @@
         <v/>
       </c>
       <c r="C54" s="15">
+        <f>IF(AND(ISNUMBER($L54),$L54&lt;&gt;""),INDEX(Data!$J:$J,$L54),"")</f>
+        <v/>
+      </c>
+      <c r="D54" s="15">
         <f>IF(AND(ISNUMBER($L54),$L54&lt;&gt;""),INDEX(Data!$K:$K,$L54),"")</f>
         <v/>
       </c>
-      <c r="D54" s="15">
+      <c r="E54" s="15">
         <f>IF(AND(ISNUMBER($L54),$L54&lt;&gt;""),IF(INDEX(Data!$L:$L,$L54)="","—",INDEX(Data!$L:$L,$L54)),"")</f>
         <v/>
       </c>
-      <c r="E54" s="15">
+      <c r="F54" s="15">
         <f>IF(AND(ISNUMBER($L54),$L54&lt;&gt;""),IF(INDEX(Data!$M:$M,$L54)="","—",INDEX(Data!$M:$M,$L54)),"")</f>
         <v/>
       </c>
-      <c r="F54" s="16">
+      <c r="G54" s="16">
         <f>IF(AND(ISNUMBER($L54),$L54&lt;&gt;""),IF(INDEX(Data!$N:$N,$L54)="","—",INDEX(Data!$N:$N,$L54)),"")</f>
         <v/>
       </c>
-      <c r="G54" s="17">
+      <c r="H54" s="17">
         <f>IF(AND(ISNUMBER($L54),$L54&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L54)="","—",INDEX(Data!$Q:$Q,$L54)),"")</f>
         <v/>
       </c>
-      <c r="H54" s="18">
+      <c r="I54" s="18">
         <f>IF(AND(ISNUMBER($L54),$L54&lt;&gt;""),INDEX(Data!$E:$E,$L54),"")</f>
         <v/>
       </c>
-      <c r="I54" s="18">
+      <c r="J54" s="18">
         <f>IF(AND(ISNUMBER($L54),$L54&lt;&gt;""),INDEX(Data!$F:$F,$L54),"")</f>
         <v/>
       </c>
@@ -2750,30 +2936,34 @@
         <v/>
       </c>
       <c r="C55" s="20">
+        <f>IF(AND(ISNUMBER($L55),$L55&lt;&gt;""),INDEX(Data!$J:$J,$L55),"")</f>
+        <v/>
+      </c>
+      <c r="D55" s="20">
         <f>IF(AND(ISNUMBER($L55),$L55&lt;&gt;""),INDEX(Data!$K:$K,$L55),"")</f>
         <v/>
       </c>
-      <c r="D55" s="20">
+      <c r="E55" s="20">
         <f>IF(AND(ISNUMBER($L55),$L55&lt;&gt;""),IF(INDEX(Data!$L:$L,$L55)="","—",INDEX(Data!$L:$L,$L55)),"")</f>
         <v/>
       </c>
-      <c r="E55" s="20">
+      <c r="F55" s="20">
         <f>IF(AND(ISNUMBER($L55),$L55&lt;&gt;""),IF(INDEX(Data!$M:$M,$L55)="","—",INDEX(Data!$M:$M,$L55)),"")</f>
         <v/>
       </c>
-      <c r="F55" s="21">
+      <c r="G55" s="21">
         <f>IF(AND(ISNUMBER($L55),$L55&lt;&gt;""),IF(INDEX(Data!$N:$N,$L55)="","—",INDEX(Data!$N:$N,$L55)),"")</f>
         <v/>
       </c>
-      <c r="G55" s="22">
+      <c r="H55" s="22">
         <f>IF(AND(ISNUMBER($L55),$L55&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L55)="","—",INDEX(Data!$Q:$Q,$L55)),"")</f>
         <v/>
       </c>
-      <c r="H55" s="23">
+      <c r="I55" s="23">
         <f>IF(AND(ISNUMBER($L55),$L55&lt;&gt;""),INDEX(Data!$E:$E,$L55),"")</f>
         <v/>
       </c>
-      <c r="I55" s="23">
+      <c r="J55" s="23">
         <f>IF(AND(ISNUMBER($L55),$L55&lt;&gt;""),INDEX(Data!$F:$F,$L55),"")</f>
         <v/>
       </c>
@@ -2792,30 +2982,34 @@
         <v/>
       </c>
       <c r="C56" s="15">
+        <f>IF(AND(ISNUMBER($L56),$L56&lt;&gt;""),INDEX(Data!$J:$J,$L56),"")</f>
+        <v/>
+      </c>
+      <c r="D56" s="15">
         <f>IF(AND(ISNUMBER($L56),$L56&lt;&gt;""),INDEX(Data!$K:$K,$L56),"")</f>
         <v/>
       </c>
-      <c r="D56" s="15">
+      <c r="E56" s="15">
         <f>IF(AND(ISNUMBER($L56),$L56&lt;&gt;""),IF(INDEX(Data!$L:$L,$L56)="","—",INDEX(Data!$L:$L,$L56)),"")</f>
         <v/>
       </c>
-      <c r="E56" s="15">
+      <c r="F56" s="15">
         <f>IF(AND(ISNUMBER($L56),$L56&lt;&gt;""),IF(INDEX(Data!$M:$M,$L56)="","—",INDEX(Data!$M:$M,$L56)),"")</f>
         <v/>
       </c>
-      <c r="F56" s="16">
+      <c r="G56" s="16">
         <f>IF(AND(ISNUMBER($L56),$L56&lt;&gt;""),IF(INDEX(Data!$N:$N,$L56)="","—",INDEX(Data!$N:$N,$L56)),"")</f>
         <v/>
       </c>
-      <c r="G56" s="17">
+      <c r="H56" s="17">
         <f>IF(AND(ISNUMBER($L56),$L56&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L56)="","—",INDEX(Data!$Q:$Q,$L56)),"")</f>
         <v/>
       </c>
-      <c r="H56" s="18">
+      <c r="I56" s="18">
         <f>IF(AND(ISNUMBER($L56),$L56&lt;&gt;""),INDEX(Data!$E:$E,$L56),"")</f>
         <v/>
       </c>
-      <c r="I56" s="18">
+      <c r="J56" s="18">
         <f>IF(AND(ISNUMBER($L56),$L56&lt;&gt;""),INDEX(Data!$F:$F,$L56),"")</f>
         <v/>
       </c>
@@ -2834,30 +3028,34 @@
         <v/>
       </c>
       <c r="C57" s="20">
+        <f>IF(AND(ISNUMBER($L57),$L57&lt;&gt;""),INDEX(Data!$J:$J,$L57),"")</f>
+        <v/>
+      </c>
+      <c r="D57" s="20">
         <f>IF(AND(ISNUMBER($L57),$L57&lt;&gt;""),INDEX(Data!$K:$K,$L57),"")</f>
         <v/>
       </c>
-      <c r="D57" s="20">
+      <c r="E57" s="20">
         <f>IF(AND(ISNUMBER($L57),$L57&lt;&gt;""),IF(INDEX(Data!$L:$L,$L57)="","—",INDEX(Data!$L:$L,$L57)),"")</f>
         <v/>
       </c>
-      <c r="E57" s="20">
+      <c r="F57" s="20">
         <f>IF(AND(ISNUMBER($L57),$L57&lt;&gt;""),IF(INDEX(Data!$M:$M,$L57)="","—",INDEX(Data!$M:$M,$L57)),"")</f>
         <v/>
       </c>
-      <c r="F57" s="21">
+      <c r="G57" s="21">
         <f>IF(AND(ISNUMBER($L57),$L57&lt;&gt;""),IF(INDEX(Data!$N:$N,$L57)="","—",INDEX(Data!$N:$N,$L57)),"")</f>
         <v/>
       </c>
-      <c r="G57" s="22">
+      <c r="H57" s="22">
         <f>IF(AND(ISNUMBER($L57),$L57&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L57)="","—",INDEX(Data!$Q:$Q,$L57)),"")</f>
         <v/>
       </c>
-      <c r="H57" s="23">
+      <c r="I57" s="23">
         <f>IF(AND(ISNUMBER($L57),$L57&lt;&gt;""),INDEX(Data!$E:$E,$L57),"")</f>
         <v/>
       </c>
-      <c r="I57" s="23">
+      <c r="J57" s="23">
         <f>IF(AND(ISNUMBER($L57),$L57&lt;&gt;""),INDEX(Data!$F:$F,$L57),"")</f>
         <v/>
       </c>
@@ -2876,30 +3074,34 @@
         <v/>
       </c>
       <c r="C58" s="15">
+        <f>IF(AND(ISNUMBER($L58),$L58&lt;&gt;""),INDEX(Data!$J:$J,$L58),"")</f>
+        <v/>
+      </c>
+      <c r="D58" s="15">
         <f>IF(AND(ISNUMBER($L58),$L58&lt;&gt;""),INDEX(Data!$K:$K,$L58),"")</f>
         <v/>
       </c>
-      <c r="D58" s="15">
+      <c r="E58" s="15">
         <f>IF(AND(ISNUMBER($L58),$L58&lt;&gt;""),IF(INDEX(Data!$L:$L,$L58)="","—",INDEX(Data!$L:$L,$L58)),"")</f>
         <v/>
       </c>
-      <c r="E58" s="15">
+      <c r="F58" s="15">
         <f>IF(AND(ISNUMBER($L58),$L58&lt;&gt;""),IF(INDEX(Data!$M:$M,$L58)="","—",INDEX(Data!$M:$M,$L58)),"")</f>
         <v/>
       </c>
-      <c r="F58" s="16">
+      <c r="G58" s="16">
         <f>IF(AND(ISNUMBER($L58),$L58&lt;&gt;""),IF(INDEX(Data!$N:$N,$L58)="","—",INDEX(Data!$N:$N,$L58)),"")</f>
         <v/>
       </c>
-      <c r="G58" s="17">
+      <c r="H58" s="17">
         <f>IF(AND(ISNUMBER($L58),$L58&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L58)="","—",INDEX(Data!$Q:$Q,$L58)),"")</f>
         <v/>
       </c>
-      <c r="H58" s="18">
+      <c r="I58" s="18">
         <f>IF(AND(ISNUMBER($L58),$L58&lt;&gt;""),INDEX(Data!$E:$E,$L58),"")</f>
         <v/>
       </c>
-      <c r="I58" s="18">
+      <c r="J58" s="18">
         <f>IF(AND(ISNUMBER($L58),$L58&lt;&gt;""),INDEX(Data!$F:$F,$L58),"")</f>
         <v/>
       </c>
@@ -2918,30 +3120,34 @@
         <v/>
       </c>
       <c r="C59" s="20">
+        <f>IF(AND(ISNUMBER($L59),$L59&lt;&gt;""),INDEX(Data!$J:$J,$L59),"")</f>
+        <v/>
+      </c>
+      <c r="D59" s="20">
         <f>IF(AND(ISNUMBER($L59),$L59&lt;&gt;""),INDEX(Data!$K:$K,$L59),"")</f>
         <v/>
       </c>
-      <c r="D59" s="20">
+      <c r="E59" s="20">
         <f>IF(AND(ISNUMBER($L59),$L59&lt;&gt;""),IF(INDEX(Data!$L:$L,$L59)="","—",INDEX(Data!$L:$L,$L59)),"")</f>
         <v/>
       </c>
-      <c r="E59" s="20">
+      <c r="F59" s="20">
         <f>IF(AND(ISNUMBER($L59),$L59&lt;&gt;""),IF(INDEX(Data!$M:$M,$L59)="","—",INDEX(Data!$M:$M,$L59)),"")</f>
         <v/>
       </c>
-      <c r="F59" s="21">
+      <c r="G59" s="21">
         <f>IF(AND(ISNUMBER($L59),$L59&lt;&gt;""),IF(INDEX(Data!$N:$N,$L59)="","—",INDEX(Data!$N:$N,$L59)),"")</f>
         <v/>
       </c>
-      <c r="G59" s="22">
+      <c r="H59" s="22">
         <f>IF(AND(ISNUMBER($L59),$L59&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L59)="","—",INDEX(Data!$Q:$Q,$L59)),"")</f>
         <v/>
       </c>
-      <c r="H59" s="23">
+      <c r="I59" s="23">
         <f>IF(AND(ISNUMBER($L59),$L59&lt;&gt;""),INDEX(Data!$E:$E,$L59),"")</f>
         <v/>
       </c>
-      <c r="I59" s="23">
+      <c r="J59" s="23">
         <f>IF(AND(ISNUMBER($L59),$L59&lt;&gt;""),INDEX(Data!$F:$F,$L59),"")</f>
         <v/>
       </c>
@@ -2960,30 +3166,34 @@
         <v/>
       </c>
       <c r="C60" s="15">
+        <f>IF(AND(ISNUMBER($L60),$L60&lt;&gt;""),INDEX(Data!$J:$J,$L60),"")</f>
+        <v/>
+      </c>
+      <c r="D60" s="15">
         <f>IF(AND(ISNUMBER($L60),$L60&lt;&gt;""),INDEX(Data!$K:$K,$L60),"")</f>
         <v/>
       </c>
-      <c r="D60" s="15">
+      <c r="E60" s="15">
         <f>IF(AND(ISNUMBER($L60),$L60&lt;&gt;""),IF(INDEX(Data!$L:$L,$L60)="","—",INDEX(Data!$L:$L,$L60)),"")</f>
         <v/>
       </c>
-      <c r="E60" s="15">
+      <c r="F60" s="15">
         <f>IF(AND(ISNUMBER($L60),$L60&lt;&gt;""),IF(INDEX(Data!$M:$M,$L60)="","—",INDEX(Data!$M:$M,$L60)),"")</f>
         <v/>
       </c>
-      <c r="F60" s="16">
+      <c r="G60" s="16">
         <f>IF(AND(ISNUMBER($L60),$L60&lt;&gt;""),IF(INDEX(Data!$N:$N,$L60)="","—",INDEX(Data!$N:$N,$L60)),"")</f>
         <v/>
       </c>
-      <c r="G60" s="17">
+      <c r="H60" s="17">
         <f>IF(AND(ISNUMBER($L60),$L60&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L60)="","—",INDEX(Data!$Q:$Q,$L60)),"")</f>
         <v/>
       </c>
-      <c r="H60" s="18">
+      <c r="I60" s="18">
         <f>IF(AND(ISNUMBER($L60),$L60&lt;&gt;""),INDEX(Data!$E:$E,$L60),"")</f>
         <v/>
       </c>
-      <c r="I60" s="18">
+      <c r="J60" s="18">
         <f>IF(AND(ISNUMBER($L60),$L60&lt;&gt;""),INDEX(Data!$F:$F,$L60),"")</f>
         <v/>
       </c>
@@ -3002,30 +3212,34 @@
         <v/>
       </c>
       <c r="C61" s="20">
+        <f>IF(AND(ISNUMBER($L61),$L61&lt;&gt;""),INDEX(Data!$J:$J,$L61),"")</f>
+        <v/>
+      </c>
+      <c r="D61" s="20">
         <f>IF(AND(ISNUMBER($L61),$L61&lt;&gt;""),INDEX(Data!$K:$K,$L61),"")</f>
         <v/>
       </c>
-      <c r="D61" s="20">
+      <c r="E61" s="20">
         <f>IF(AND(ISNUMBER($L61),$L61&lt;&gt;""),IF(INDEX(Data!$L:$L,$L61)="","—",INDEX(Data!$L:$L,$L61)),"")</f>
         <v/>
       </c>
-      <c r="E61" s="20">
+      <c r="F61" s="20">
         <f>IF(AND(ISNUMBER($L61),$L61&lt;&gt;""),IF(INDEX(Data!$M:$M,$L61)="","—",INDEX(Data!$M:$M,$L61)),"")</f>
         <v/>
       </c>
-      <c r="F61" s="21">
+      <c r="G61" s="21">
         <f>IF(AND(ISNUMBER($L61),$L61&lt;&gt;""),IF(INDEX(Data!$N:$N,$L61)="","—",INDEX(Data!$N:$N,$L61)),"")</f>
         <v/>
       </c>
-      <c r="G61" s="22">
+      <c r="H61" s="22">
         <f>IF(AND(ISNUMBER($L61),$L61&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L61)="","—",INDEX(Data!$Q:$Q,$L61)),"")</f>
         <v/>
       </c>
-      <c r="H61" s="23">
+      <c r="I61" s="23">
         <f>IF(AND(ISNUMBER($L61),$L61&lt;&gt;""),INDEX(Data!$E:$E,$L61),"")</f>
         <v/>
       </c>
-      <c r="I61" s="23">
+      <c r="J61" s="23">
         <f>IF(AND(ISNUMBER($L61),$L61&lt;&gt;""),INDEX(Data!$F:$F,$L61),"")</f>
         <v/>
       </c>
@@ -3044,30 +3258,34 @@
         <v/>
       </c>
       <c r="C62" s="15">
+        <f>IF(AND(ISNUMBER($L62),$L62&lt;&gt;""),INDEX(Data!$J:$J,$L62),"")</f>
+        <v/>
+      </c>
+      <c r="D62" s="15">
         <f>IF(AND(ISNUMBER($L62),$L62&lt;&gt;""),INDEX(Data!$K:$K,$L62),"")</f>
         <v/>
       </c>
-      <c r="D62" s="15">
+      <c r="E62" s="15">
         <f>IF(AND(ISNUMBER($L62),$L62&lt;&gt;""),IF(INDEX(Data!$L:$L,$L62)="","—",INDEX(Data!$L:$L,$L62)),"")</f>
         <v/>
       </c>
-      <c r="E62" s="15">
+      <c r="F62" s="15">
         <f>IF(AND(ISNUMBER($L62),$L62&lt;&gt;""),IF(INDEX(Data!$M:$M,$L62)="","—",INDEX(Data!$M:$M,$L62)),"")</f>
         <v/>
       </c>
-      <c r="F62" s="16">
+      <c r="G62" s="16">
         <f>IF(AND(ISNUMBER($L62),$L62&lt;&gt;""),IF(INDEX(Data!$N:$N,$L62)="","—",INDEX(Data!$N:$N,$L62)),"")</f>
         <v/>
       </c>
-      <c r="G62" s="17">
+      <c r="H62" s="17">
         <f>IF(AND(ISNUMBER($L62),$L62&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L62)="","—",INDEX(Data!$Q:$Q,$L62)),"")</f>
         <v/>
       </c>
-      <c r="H62" s="18">
+      <c r="I62" s="18">
         <f>IF(AND(ISNUMBER($L62),$L62&lt;&gt;""),INDEX(Data!$E:$E,$L62),"")</f>
         <v/>
       </c>
-      <c r="I62" s="18">
+      <c r="J62" s="18">
         <f>IF(AND(ISNUMBER($L62),$L62&lt;&gt;""),INDEX(Data!$F:$F,$L62),"")</f>
         <v/>
       </c>
@@ -3086,30 +3304,34 @@
         <v/>
       </c>
       <c r="C63" s="20">
+        <f>IF(AND(ISNUMBER($L63),$L63&lt;&gt;""),INDEX(Data!$J:$J,$L63),"")</f>
+        <v/>
+      </c>
+      <c r="D63" s="20">
         <f>IF(AND(ISNUMBER($L63),$L63&lt;&gt;""),INDEX(Data!$K:$K,$L63),"")</f>
         <v/>
       </c>
-      <c r="D63" s="20">
+      <c r="E63" s="20">
         <f>IF(AND(ISNUMBER($L63),$L63&lt;&gt;""),IF(INDEX(Data!$L:$L,$L63)="","—",INDEX(Data!$L:$L,$L63)),"")</f>
         <v/>
       </c>
-      <c r="E63" s="20">
+      <c r="F63" s="20">
         <f>IF(AND(ISNUMBER($L63),$L63&lt;&gt;""),IF(INDEX(Data!$M:$M,$L63)="","—",INDEX(Data!$M:$M,$L63)),"")</f>
         <v/>
       </c>
-      <c r="F63" s="21">
+      <c r="G63" s="21">
         <f>IF(AND(ISNUMBER($L63),$L63&lt;&gt;""),IF(INDEX(Data!$N:$N,$L63)="","—",INDEX(Data!$N:$N,$L63)),"")</f>
         <v/>
       </c>
-      <c r="G63" s="22">
+      <c r="H63" s="22">
         <f>IF(AND(ISNUMBER($L63),$L63&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L63)="","—",INDEX(Data!$Q:$Q,$L63)),"")</f>
         <v/>
       </c>
-      <c r="H63" s="23">
+      <c r="I63" s="23">
         <f>IF(AND(ISNUMBER($L63),$L63&lt;&gt;""),INDEX(Data!$E:$E,$L63),"")</f>
         <v/>
       </c>
-      <c r="I63" s="23">
+      <c r="J63" s="23">
         <f>IF(AND(ISNUMBER($L63),$L63&lt;&gt;""),INDEX(Data!$F:$F,$L63),"")</f>
         <v/>
       </c>
@@ -3128,30 +3350,34 @@
         <v/>
       </c>
       <c r="C64" s="15">
+        <f>IF(AND(ISNUMBER($L64),$L64&lt;&gt;""),INDEX(Data!$J:$J,$L64),"")</f>
+        <v/>
+      </c>
+      <c r="D64" s="15">
         <f>IF(AND(ISNUMBER($L64),$L64&lt;&gt;""),INDEX(Data!$K:$K,$L64),"")</f>
         <v/>
       </c>
-      <c r="D64" s="15">
+      <c r="E64" s="15">
         <f>IF(AND(ISNUMBER($L64),$L64&lt;&gt;""),IF(INDEX(Data!$L:$L,$L64)="","—",INDEX(Data!$L:$L,$L64)),"")</f>
         <v/>
       </c>
-      <c r="E64" s="15">
+      <c r="F64" s="15">
         <f>IF(AND(ISNUMBER($L64),$L64&lt;&gt;""),IF(INDEX(Data!$M:$M,$L64)="","—",INDEX(Data!$M:$M,$L64)),"")</f>
         <v/>
       </c>
-      <c r="F64" s="16">
+      <c r="G64" s="16">
         <f>IF(AND(ISNUMBER($L64),$L64&lt;&gt;""),IF(INDEX(Data!$N:$N,$L64)="","—",INDEX(Data!$N:$N,$L64)),"")</f>
         <v/>
       </c>
-      <c r="G64" s="17">
+      <c r="H64" s="17">
         <f>IF(AND(ISNUMBER($L64),$L64&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L64)="","—",INDEX(Data!$Q:$Q,$L64)),"")</f>
         <v/>
       </c>
-      <c r="H64" s="18">
+      <c r="I64" s="18">
         <f>IF(AND(ISNUMBER($L64),$L64&lt;&gt;""),INDEX(Data!$E:$E,$L64),"")</f>
         <v/>
       </c>
-      <c r="I64" s="18">
+      <c r="J64" s="18">
         <f>IF(AND(ISNUMBER($L64),$L64&lt;&gt;""),INDEX(Data!$F:$F,$L64),"")</f>
         <v/>
       </c>
@@ -3170,30 +3396,34 @@
         <v/>
       </c>
       <c r="C65" s="20">
+        <f>IF(AND(ISNUMBER($L65),$L65&lt;&gt;""),INDEX(Data!$J:$J,$L65),"")</f>
+        <v/>
+      </c>
+      <c r="D65" s="20">
         <f>IF(AND(ISNUMBER($L65),$L65&lt;&gt;""),INDEX(Data!$K:$K,$L65),"")</f>
         <v/>
       </c>
-      <c r="D65" s="20">
+      <c r="E65" s="20">
         <f>IF(AND(ISNUMBER($L65),$L65&lt;&gt;""),IF(INDEX(Data!$L:$L,$L65)="","—",INDEX(Data!$L:$L,$L65)),"")</f>
         <v/>
       </c>
-      <c r="E65" s="20">
+      <c r="F65" s="20">
         <f>IF(AND(ISNUMBER($L65),$L65&lt;&gt;""),IF(INDEX(Data!$M:$M,$L65)="","—",INDEX(Data!$M:$M,$L65)),"")</f>
         <v/>
       </c>
-      <c r="F65" s="21">
+      <c r="G65" s="21">
         <f>IF(AND(ISNUMBER($L65),$L65&lt;&gt;""),IF(INDEX(Data!$N:$N,$L65)="","—",INDEX(Data!$N:$N,$L65)),"")</f>
         <v/>
       </c>
-      <c r="G65" s="22">
+      <c r="H65" s="22">
         <f>IF(AND(ISNUMBER($L65),$L65&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L65)="","—",INDEX(Data!$Q:$Q,$L65)),"")</f>
         <v/>
       </c>
-      <c r="H65" s="23">
+      <c r="I65" s="23">
         <f>IF(AND(ISNUMBER($L65),$L65&lt;&gt;""),INDEX(Data!$E:$E,$L65),"")</f>
         <v/>
       </c>
-      <c r="I65" s="23">
+      <c r="J65" s="23">
         <f>IF(AND(ISNUMBER($L65),$L65&lt;&gt;""),INDEX(Data!$F:$F,$L65),"")</f>
         <v/>
       </c>
@@ -3212,30 +3442,34 @@
         <v/>
       </c>
       <c r="C66" s="15">
+        <f>IF(AND(ISNUMBER($L66),$L66&lt;&gt;""),INDEX(Data!$J:$J,$L66),"")</f>
+        <v/>
+      </c>
+      <c r="D66" s="15">
         <f>IF(AND(ISNUMBER($L66),$L66&lt;&gt;""),INDEX(Data!$K:$K,$L66),"")</f>
         <v/>
       </c>
-      <c r="D66" s="15">
+      <c r="E66" s="15">
         <f>IF(AND(ISNUMBER($L66),$L66&lt;&gt;""),IF(INDEX(Data!$L:$L,$L66)="","—",INDEX(Data!$L:$L,$L66)),"")</f>
         <v/>
       </c>
-      <c r="E66" s="15">
+      <c r="F66" s="15">
         <f>IF(AND(ISNUMBER($L66),$L66&lt;&gt;""),IF(INDEX(Data!$M:$M,$L66)="","—",INDEX(Data!$M:$M,$L66)),"")</f>
         <v/>
       </c>
-      <c r="F66" s="16">
+      <c r="G66" s="16">
         <f>IF(AND(ISNUMBER($L66),$L66&lt;&gt;""),IF(INDEX(Data!$N:$N,$L66)="","—",INDEX(Data!$N:$N,$L66)),"")</f>
         <v/>
       </c>
-      <c r="G66" s="17">
+      <c r="H66" s="17">
         <f>IF(AND(ISNUMBER($L66),$L66&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L66)="","—",INDEX(Data!$Q:$Q,$L66)),"")</f>
         <v/>
       </c>
-      <c r="H66" s="18">
+      <c r="I66" s="18">
         <f>IF(AND(ISNUMBER($L66),$L66&lt;&gt;""),INDEX(Data!$E:$E,$L66),"")</f>
         <v/>
       </c>
-      <c r="I66" s="18">
+      <c r="J66" s="18">
         <f>IF(AND(ISNUMBER($L66),$L66&lt;&gt;""),INDEX(Data!$F:$F,$L66),"")</f>
         <v/>
       </c>
@@ -3254,30 +3488,34 @@
         <v/>
       </c>
       <c r="C67" s="20">
+        <f>IF(AND(ISNUMBER($L67),$L67&lt;&gt;""),INDEX(Data!$J:$J,$L67),"")</f>
+        <v/>
+      </c>
+      <c r="D67" s="20">
         <f>IF(AND(ISNUMBER($L67),$L67&lt;&gt;""),INDEX(Data!$K:$K,$L67),"")</f>
         <v/>
       </c>
-      <c r="D67" s="20">
+      <c r="E67" s="20">
         <f>IF(AND(ISNUMBER($L67),$L67&lt;&gt;""),IF(INDEX(Data!$L:$L,$L67)="","—",INDEX(Data!$L:$L,$L67)),"")</f>
         <v/>
       </c>
-      <c r="E67" s="20">
+      <c r="F67" s="20">
         <f>IF(AND(ISNUMBER($L67),$L67&lt;&gt;""),IF(INDEX(Data!$M:$M,$L67)="","—",INDEX(Data!$M:$M,$L67)),"")</f>
         <v/>
       </c>
-      <c r="F67" s="21">
+      <c r="G67" s="21">
         <f>IF(AND(ISNUMBER($L67),$L67&lt;&gt;""),IF(INDEX(Data!$N:$N,$L67)="","—",INDEX(Data!$N:$N,$L67)),"")</f>
         <v/>
       </c>
-      <c r="G67" s="22">
+      <c r="H67" s="22">
         <f>IF(AND(ISNUMBER($L67),$L67&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L67)="","—",INDEX(Data!$Q:$Q,$L67)),"")</f>
         <v/>
       </c>
-      <c r="H67" s="23">
+      <c r="I67" s="23">
         <f>IF(AND(ISNUMBER($L67),$L67&lt;&gt;""),INDEX(Data!$E:$E,$L67),"")</f>
         <v/>
       </c>
-      <c r="I67" s="23">
+      <c r="J67" s="23">
         <f>IF(AND(ISNUMBER($L67),$L67&lt;&gt;""),INDEX(Data!$F:$F,$L67),"")</f>
         <v/>
       </c>
@@ -3296,30 +3534,34 @@
         <v/>
       </c>
       <c r="C68" s="15">
+        <f>IF(AND(ISNUMBER($L68),$L68&lt;&gt;""),INDEX(Data!$J:$J,$L68),"")</f>
+        <v/>
+      </c>
+      <c r="D68" s="15">
         <f>IF(AND(ISNUMBER($L68),$L68&lt;&gt;""),INDEX(Data!$K:$K,$L68),"")</f>
         <v/>
       </c>
-      <c r="D68" s="15">
+      <c r="E68" s="15">
         <f>IF(AND(ISNUMBER($L68),$L68&lt;&gt;""),IF(INDEX(Data!$L:$L,$L68)="","—",INDEX(Data!$L:$L,$L68)),"")</f>
         <v/>
       </c>
-      <c r="E68" s="15">
+      <c r="F68" s="15">
         <f>IF(AND(ISNUMBER($L68),$L68&lt;&gt;""),IF(INDEX(Data!$M:$M,$L68)="","—",INDEX(Data!$M:$M,$L68)),"")</f>
         <v/>
       </c>
-      <c r="F68" s="16">
+      <c r="G68" s="16">
         <f>IF(AND(ISNUMBER($L68),$L68&lt;&gt;""),IF(INDEX(Data!$N:$N,$L68)="","—",INDEX(Data!$N:$N,$L68)),"")</f>
         <v/>
       </c>
-      <c r="G68" s="17">
+      <c r="H68" s="17">
         <f>IF(AND(ISNUMBER($L68),$L68&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L68)="","—",INDEX(Data!$Q:$Q,$L68)),"")</f>
         <v/>
       </c>
-      <c r="H68" s="18">
+      <c r="I68" s="18">
         <f>IF(AND(ISNUMBER($L68),$L68&lt;&gt;""),INDEX(Data!$E:$E,$L68),"")</f>
         <v/>
       </c>
-      <c r="I68" s="18">
+      <c r="J68" s="18">
         <f>IF(AND(ISNUMBER($L68),$L68&lt;&gt;""),INDEX(Data!$F:$F,$L68),"")</f>
         <v/>
       </c>
@@ -3338,30 +3580,34 @@
         <v/>
       </c>
       <c r="C69" s="20">
+        <f>IF(AND(ISNUMBER($L69),$L69&lt;&gt;""),INDEX(Data!$J:$J,$L69),"")</f>
+        <v/>
+      </c>
+      <c r="D69" s="20">
         <f>IF(AND(ISNUMBER($L69),$L69&lt;&gt;""),INDEX(Data!$K:$K,$L69),"")</f>
         <v/>
       </c>
-      <c r="D69" s="20">
+      <c r="E69" s="20">
         <f>IF(AND(ISNUMBER($L69),$L69&lt;&gt;""),IF(INDEX(Data!$L:$L,$L69)="","—",INDEX(Data!$L:$L,$L69)),"")</f>
         <v/>
       </c>
-      <c r="E69" s="20">
+      <c r="F69" s="20">
         <f>IF(AND(ISNUMBER($L69),$L69&lt;&gt;""),IF(INDEX(Data!$M:$M,$L69)="","—",INDEX(Data!$M:$M,$L69)),"")</f>
         <v/>
       </c>
-      <c r="F69" s="21">
+      <c r="G69" s="21">
         <f>IF(AND(ISNUMBER($L69),$L69&lt;&gt;""),IF(INDEX(Data!$N:$N,$L69)="","—",INDEX(Data!$N:$N,$L69)),"")</f>
         <v/>
       </c>
-      <c r="G69" s="22">
+      <c r="H69" s="22">
         <f>IF(AND(ISNUMBER($L69),$L69&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L69)="","—",INDEX(Data!$Q:$Q,$L69)),"")</f>
         <v/>
       </c>
-      <c r="H69" s="23">
+      <c r="I69" s="23">
         <f>IF(AND(ISNUMBER($L69),$L69&lt;&gt;""),INDEX(Data!$E:$E,$L69),"")</f>
         <v/>
       </c>
-      <c r="I69" s="23">
+      <c r="J69" s="23">
         <f>IF(AND(ISNUMBER($L69),$L69&lt;&gt;""),INDEX(Data!$F:$F,$L69),"")</f>
         <v/>
       </c>
@@ -3380,30 +3626,34 @@
         <v/>
       </c>
       <c r="C70" s="15">
+        <f>IF(AND(ISNUMBER($L70),$L70&lt;&gt;""),INDEX(Data!$J:$J,$L70),"")</f>
+        <v/>
+      </c>
+      <c r="D70" s="15">
         <f>IF(AND(ISNUMBER($L70),$L70&lt;&gt;""),INDEX(Data!$K:$K,$L70),"")</f>
         <v/>
       </c>
-      <c r="D70" s="15">
+      <c r="E70" s="15">
         <f>IF(AND(ISNUMBER($L70),$L70&lt;&gt;""),IF(INDEX(Data!$L:$L,$L70)="","—",INDEX(Data!$L:$L,$L70)),"")</f>
         <v/>
       </c>
-      <c r="E70" s="15">
+      <c r="F70" s="15">
         <f>IF(AND(ISNUMBER($L70),$L70&lt;&gt;""),IF(INDEX(Data!$M:$M,$L70)="","—",INDEX(Data!$M:$M,$L70)),"")</f>
         <v/>
       </c>
-      <c r="F70" s="16">
+      <c r="G70" s="16">
         <f>IF(AND(ISNUMBER($L70),$L70&lt;&gt;""),IF(INDEX(Data!$N:$N,$L70)="","—",INDEX(Data!$N:$N,$L70)),"")</f>
         <v/>
       </c>
-      <c r="G70" s="17">
+      <c r="H70" s="17">
         <f>IF(AND(ISNUMBER($L70),$L70&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L70)="","—",INDEX(Data!$Q:$Q,$L70)),"")</f>
         <v/>
       </c>
-      <c r="H70" s="18">
+      <c r="I70" s="18">
         <f>IF(AND(ISNUMBER($L70),$L70&lt;&gt;""),INDEX(Data!$E:$E,$L70),"")</f>
         <v/>
       </c>
-      <c r="I70" s="18">
+      <c r="J70" s="18">
         <f>IF(AND(ISNUMBER($L70),$L70&lt;&gt;""),INDEX(Data!$F:$F,$L70),"")</f>
         <v/>
       </c>
@@ -3422,30 +3672,34 @@
         <v/>
       </c>
       <c r="C71" s="20">
+        <f>IF(AND(ISNUMBER($L71),$L71&lt;&gt;""),INDEX(Data!$J:$J,$L71),"")</f>
+        <v/>
+      </c>
+      <c r="D71" s="20">
         <f>IF(AND(ISNUMBER($L71),$L71&lt;&gt;""),INDEX(Data!$K:$K,$L71),"")</f>
         <v/>
       </c>
-      <c r="D71" s="20">
+      <c r="E71" s="20">
         <f>IF(AND(ISNUMBER($L71),$L71&lt;&gt;""),IF(INDEX(Data!$L:$L,$L71)="","—",INDEX(Data!$L:$L,$L71)),"")</f>
         <v/>
       </c>
-      <c r="E71" s="20">
+      <c r="F71" s="20">
         <f>IF(AND(ISNUMBER($L71),$L71&lt;&gt;""),IF(INDEX(Data!$M:$M,$L71)="","—",INDEX(Data!$M:$M,$L71)),"")</f>
         <v/>
       </c>
-      <c r="F71" s="21">
+      <c r="G71" s="21">
         <f>IF(AND(ISNUMBER($L71),$L71&lt;&gt;""),IF(INDEX(Data!$N:$N,$L71)="","—",INDEX(Data!$N:$N,$L71)),"")</f>
         <v/>
       </c>
-      <c r="G71" s="22">
+      <c r="H71" s="22">
         <f>IF(AND(ISNUMBER($L71),$L71&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L71)="","—",INDEX(Data!$Q:$Q,$L71)),"")</f>
         <v/>
       </c>
-      <c r="H71" s="23">
+      <c r="I71" s="23">
         <f>IF(AND(ISNUMBER($L71),$L71&lt;&gt;""),INDEX(Data!$E:$E,$L71),"")</f>
         <v/>
       </c>
-      <c r="I71" s="23">
+      <c r="J71" s="23">
         <f>IF(AND(ISNUMBER($L71),$L71&lt;&gt;""),INDEX(Data!$F:$F,$L71),"")</f>
         <v/>
       </c>
@@ -3464,30 +3718,34 @@
         <v/>
       </c>
       <c r="C72" s="15">
+        <f>IF(AND(ISNUMBER($L72),$L72&lt;&gt;""),INDEX(Data!$J:$J,$L72),"")</f>
+        <v/>
+      </c>
+      <c r="D72" s="15">
         <f>IF(AND(ISNUMBER($L72),$L72&lt;&gt;""),INDEX(Data!$K:$K,$L72),"")</f>
         <v/>
       </c>
-      <c r="D72" s="15">
+      <c r="E72" s="15">
         <f>IF(AND(ISNUMBER($L72),$L72&lt;&gt;""),IF(INDEX(Data!$L:$L,$L72)="","—",INDEX(Data!$L:$L,$L72)),"")</f>
         <v/>
       </c>
-      <c r="E72" s="15">
+      <c r="F72" s="15">
         <f>IF(AND(ISNUMBER($L72),$L72&lt;&gt;""),IF(INDEX(Data!$M:$M,$L72)="","—",INDEX(Data!$M:$M,$L72)),"")</f>
         <v/>
       </c>
-      <c r="F72" s="16">
+      <c r="G72" s="16">
         <f>IF(AND(ISNUMBER($L72),$L72&lt;&gt;""),IF(INDEX(Data!$N:$N,$L72)="","—",INDEX(Data!$N:$N,$L72)),"")</f>
         <v/>
       </c>
-      <c r="G72" s="17">
+      <c r="H72" s="17">
         <f>IF(AND(ISNUMBER($L72),$L72&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L72)="","—",INDEX(Data!$Q:$Q,$L72)),"")</f>
         <v/>
       </c>
-      <c r="H72" s="18">
+      <c r="I72" s="18">
         <f>IF(AND(ISNUMBER($L72),$L72&lt;&gt;""),INDEX(Data!$E:$E,$L72),"")</f>
         <v/>
       </c>
-      <c r="I72" s="18">
+      <c r="J72" s="18">
         <f>IF(AND(ISNUMBER($L72),$L72&lt;&gt;""),INDEX(Data!$F:$F,$L72),"")</f>
         <v/>
       </c>
@@ -3506,30 +3764,34 @@
         <v/>
       </c>
       <c r="C73" s="20">
+        <f>IF(AND(ISNUMBER($L73),$L73&lt;&gt;""),INDEX(Data!$J:$J,$L73),"")</f>
+        <v/>
+      </c>
+      <c r="D73" s="20">
         <f>IF(AND(ISNUMBER($L73),$L73&lt;&gt;""),INDEX(Data!$K:$K,$L73),"")</f>
         <v/>
       </c>
-      <c r="D73" s="20">
+      <c r="E73" s="20">
         <f>IF(AND(ISNUMBER($L73),$L73&lt;&gt;""),IF(INDEX(Data!$L:$L,$L73)="","—",INDEX(Data!$L:$L,$L73)),"")</f>
         <v/>
       </c>
-      <c r="E73" s="20">
+      <c r="F73" s="20">
         <f>IF(AND(ISNUMBER($L73),$L73&lt;&gt;""),IF(INDEX(Data!$M:$M,$L73)="","—",INDEX(Data!$M:$M,$L73)),"")</f>
         <v/>
       </c>
-      <c r="F73" s="21">
+      <c r="G73" s="21">
         <f>IF(AND(ISNUMBER($L73),$L73&lt;&gt;""),IF(INDEX(Data!$N:$N,$L73)="","—",INDEX(Data!$N:$N,$L73)),"")</f>
         <v/>
       </c>
-      <c r="G73" s="22">
+      <c r="H73" s="22">
         <f>IF(AND(ISNUMBER($L73),$L73&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L73)="","—",INDEX(Data!$Q:$Q,$L73)),"")</f>
         <v/>
       </c>
-      <c r="H73" s="23">
+      <c r="I73" s="23">
         <f>IF(AND(ISNUMBER($L73),$L73&lt;&gt;""),INDEX(Data!$E:$E,$L73),"")</f>
         <v/>
       </c>
-      <c r="I73" s="23">
+      <c r="J73" s="23">
         <f>IF(AND(ISNUMBER($L73),$L73&lt;&gt;""),INDEX(Data!$F:$F,$L73),"")</f>
         <v/>
       </c>
@@ -3548,30 +3810,34 @@
         <v/>
       </c>
       <c r="C74" s="15">
+        <f>IF(AND(ISNUMBER($L74),$L74&lt;&gt;""),INDEX(Data!$J:$J,$L74),"")</f>
+        <v/>
+      </c>
+      <c r="D74" s="15">
         <f>IF(AND(ISNUMBER($L74),$L74&lt;&gt;""),INDEX(Data!$K:$K,$L74),"")</f>
         <v/>
       </c>
-      <c r="D74" s="15">
+      <c r="E74" s="15">
         <f>IF(AND(ISNUMBER($L74),$L74&lt;&gt;""),IF(INDEX(Data!$L:$L,$L74)="","—",INDEX(Data!$L:$L,$L74)),"")</f>
         <v/>
       </c>
-      <c r="E74" s="15">
+      <c r="F74" s="15">
         <f>IF(AND(ISNUMBER($L74),$L74&lt;&gt;""),IF(INDEX(Data!$M:$M,$L74)="","—",INDEX(Data!$M:$M,$L74)),"")</f>
         <v/>
       </c>
-      <c r="F74" s="16">
+      <c r="G74" s="16">
         <f>IF(AND(ISNUMBER($L74),$L74&lt;&gt;""),IF(INDEX(Data!$N:$N,$L74)="","—",INDEX(Data!$N:$N,$L74)),"")</f>
         <v/>
       </c>
-      <c r="G74" s="17">
+      <c r="H74" s="17">
         <f>IF(AND(ISNUMBER($L74),$L74&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L74)="","—",INDEX(Data!$Q:$Q,$L74)),"")</f>
         <v/>
       </c>
-      <c r="H74" s="18">
+      <c r="I74" s="18">
         <f>IF(AND(ISNUMBER($L74),$L74&lt;&gt;""),INDEX(Data!$E:$E,$L74),"")</f>
         <v/>
       </c>
-      <c r="I74" s="18">
+      <c r="J74" s="18">
         <f>IF(AND(ISNUMBER($L74),$L74&lt;&gt;""),INDEX(Data!$F:$F,$L74),"")</f>
         <v/>
       </c>
@@ -3590,30 +3856,34 @@
         <v/>
       </c>
       <c r="C75" s="20">
+        <f>IF(AND(ISNUMBER($L75),$L75&lt;&gt;""),INDEX(Data!$J:$J,$L75),"")</f>
+        <v/>
+      </c>
+      <c r="D75" s="20">
         <f>IF(AND(ISNUMBER($L75),$L75&lt;&gt;""),INDEX(Data!$K:$K,$L75),"")</f>
         <v/>
       </c>
-      <c r="D75" s="20">
+      <c r="E75" s="20">
         <f>IF(AND(ISNUMBER($L75),$L75&lt;&gt;""),IF(INDEX(Data!$L:$L,$L75)="","—",INDEX(Data!$L:$L,$L75)),"")</f>
         <v/>
       </c>
-      <c r="E75" s="20">
+      <c r="F75" s="20">
         <f>IF(AND(ISNUMBER($L75),$L75&lt;&gt;""),IF(INDEX(Data!$M:$M,$L75)="","—",INDEX(Data!$M:$M,$L75)),"")</f>
         <v/>
       </c>
-      <c r="F75" s="21">
+      <c r="G75" s="21">
         <f>IF(AND(ISNUMBER($L75),$L75&lt;&gt;""),IF(INDEX(Data!$N:$N,$L75)="","—",INDEX(Data!$N:$N,$L75)),"")</f>
         <v/>
       </c>
-      <c r="G75" s="22">
+      <c r="H75" s="22">
         <f>IF(AND(ISNUMBER($L75),$L75&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L75)="","—",INDEX(Data!$Q:$Q,$L75)),"")</f>
         <v/>
       </c>
-      <c r="H75" s="23">
+      <c r="I75" s="23">
         <f>IF(AND(ISNUMBER($L75),$L75&lt;&gt;""),INDEX(Data!$E:$E,$L75),"")</f>
         <v/>
       </c>
-      <c r="I75" s="23">
+      <c r="J75" s="23">
         <f>IF(AND(ISNUMBER($L75),$L75&lt;&gt;""),INDEX(Data!$F:$F,$L75),"")</f>
         <v/>
       </c>
@@ -3632,30 +3902,34 @@
         <v/>
       </c>
       <c r="C76" s="15">
+        <f>IF(AND(ISNUMBER($L76),$L76&lt;&gt;""),INDEX(Data!$J:$J,$L76),"")</f>
+        <v/>
+      </c>
+      <c r="D76" s="15">
         <f>IF(AND(ISNUMBER($L76),$L76&lt;&gt;""),INDEX(Data!$K:$K,$L76),"")</f>
         <v/>
       </c>
-      <c r="D76" s="15">
+      <c r="E76" s="15">
         <f>IF(AND(ISNUMBER($L76),$L76&lt;&gt;""),IF(INDEX(Data!$L:$L,$L76)="","—",INDEX(Data!$L:$L,$L76)),"")</f>
         <v/>
       </c>
-      <c r="E76" s="15">
+      <c r="F76" s="15">
         <f>IF(AND(ISNUMBER($L76),$L76&lt;&gt;""),IF(INDEX(Data!$M:$M,$L76)="","—",INDEX(Data!$M:$M,$L76)),"")</f>
         <v/>
       </c>
-      <c r="F76" s="16">
+      <c r="G76" s="16">
         <f>IF(AND(ISNUMBER($L76),$L76&lt;&gt;""),IF(INDEX(Data!$N:$N,$L76)="","—",INDEX(Data!$N:$N,$L76)),"")</f>
         <v/>
       </c>
-      <c r="G76" s="17">
+      <c r="H76" s="17">
         <f>IF(AND(ISNUMBER($L76),$L76&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L76)="","—",INDEX(Data!$Q:$Q,$L76)),"")</f>
         <v/>
       </c>
-      <c r="H76" s="18">
+      <c r="I76" s="18">
         <f>IF(AND(ISNUMBER($L76),$L76&lt;&gt;""),INDEX(Data!$E:$E,$L76),"")</f>
         <v/>
       </c>
-      <c r="I76" s="18">
+      <c r="J76" s="18">
         <f>IF(AND(ISNUMBER($L76),$L76&lt;&gt;""),INDEX(Data!$F:$F,$L76),"")</f>
         <v/>
       </c>
@@ -3674,30 +3948,34 @@
         <v/>
       </c>
       <c r="C77" s="20">
+        <f>IF(AND(ISNUMBER($L77),$L77&lt;&gt;""),INDEX(Data!$J:$J,$L77),"")</f>
+        <v/>
+      </c>
+      <c r="D77" s="20">
         <f>IF(AND(ISNUMBER($L77),$L77&lt;&gt;""),INDEX(Data!$K:$K,$L77),"")</f>
         <v/>
       </c>
-      <c r="D77" s="20">
+      <c r="E77" s="20">
         <f>IF(AND(ISNUMBER($L77),$L77&lt;&gt;""),IF(INDEX(Data!$L:$L,$L77)="","—",INDEX(Data!$L:$L,$L77)),"")</f>
         <v/>
       </c>
-      <c r="E77" s="20">
+      <c r="F77" s="20">
         <f>IF(AND(ISNUMBER($L77),$L77&lt;&gt;""),IF(INDEX(Data!$M:$M,$L77)="","—",INDEX(Data!$M:$M,$L77)),"")</f>
         <v/>
       </c>
-      <c r="F77" s="21">
+      <c r="G77" s="21">
         <f>IF(AND(ISNUMBER($L77),$L77&lt;&gt;""),IF(INDEX(Data!$N:$N,$L77)="","—",INDEX(Data!$N:$N,$L77)),"")</f>
         <v/>
       </c>
-      <c r="G77" s="22">
+      <c r="H77" s="22">
         <f>IF(AND(ISNUMBER($L77),$L77&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L77)="","—",INDEX(Data!$Q:$Q,$L77)),"")</f>
         <v/>
       </c>
-      <c r="H77" s="23">
+      <c r="I77" s="23">
         <f>IF(AND(ISNUMBER($L77),$L77&lt;&gt;""),INDEX(Data!$E:$E,$L77),"")</f>
         <v/>
       </c>
-      <c r="I77" s="23">
+      <c r="J77" s="23">
         <f>IF(AND(ISNUMBER($L77),$L77&lt;&gt;""),INDEX(Data!$F:$F,$L77),"")</f>
         <v/>
       </c>
@@ -3716,30 +3994,34 @@
         <v/>
       </c>
       <c r="C78" s="15">
+        <f>IF(AND(ISNUMBER($L78),$L78&lt;&gt;""),INDEX(Data!$J:$J,$L78),"")</f>
+        <v/>
+      </c>
+      <c r="D78" s="15">
         <f>IF(AND(ISNUMBER($L78),$L78&lt;&gt;""),INDEX(Data!$K:$K,$L78),"")</f>
         <v/>
       </c>
-      <c r="D78" s="15">
+      <c r="E78" s="15">
         <f>IF(AND(ISNUMBER($L78),$L78&lt;&gt;""),IF(INDEX(Data!$L:$L,$L78)="","—",INDEX(Data!$L:$L,$L78)),"")</f>
         <v/>
       </c>
-      <c r="E78" s="15">
+      <c r="F78" s="15">
         <f>IF(AND(ISNUMBER($L78),$L78&lt;&gt;""),IF(INDEX(Data!$M:$M,$L78)="","—",INDEX(Data!$M:$M,$L78)),"")</f>
         <v/>
       </c>
-      <c r="F78" s="16">
+      <c r="G78" s="16">
         <f>IF(AND(ISNUMBER($L78),$L78&lt;&gt;""),IF(INDEX(Data!$N:$N,$L78)="","—",INDEX(Data!$N:$N,$L78)),"")</f>
         <v/>
       </c>
-      <c r="G78" s="17">
+      <c r="H78" s="17">
         <f>IF(AND(ISNUMBER($L78),$L78&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L78)="","—",INDEX(Data!$Q:$Q,$L78)),"")</f>
         <v/>
       </c>
-      <c r="H78" s="18">
+      <c r="I78" s="18">
         <f>IF(AND(ISNUMBER($L78),$L78&lt;&gt;""),INDEX(Data!$E:$E,$L78),"")</f>
         <v/>
       </c>
-      <c r="I78" s="18">
+      <c r="J78" s="18">
         <f>IF(AND(ISNUMBER($L78),$L78&lt;&gt;""),INDEX(Data!$F:$F,$L78),"")</f>
         <v/>
       </c>
@@ -3758,30 +4040,34 @@
         <v/>
       </c>
       <c r="C79" s="20">
+        <f>IF(AND(ISNUMBER($L79),$L79&lt;&gt;""),INDEX(Data!$J:$J,$L79),"")</f>
+        <v/>
+      </c>
+      <c r="D79" s="20">
         <f>IF(AND(ISNUMBER($L79),$L79&lt;&gt;""),INDEX(Data!$K:$K,$L79),"")</f>
         <v/>
       </c>
-      <c r="D79" s="20">
+      <c r="E79" s="20">
         <f>IF(AND(ISNUMBER($L79),$L79&lt;&gt;""),IF(INDEX(Data!$L:$L,$L79)="","—",INDEX(Data!$L:$L,$L79)),"")</f>
         <v/>
       </c>
-      <c r="E79" s="20">
+      <c r="F79" s="20">
         <f>IF(AND(ISNUMBER($L79),$L79&lt;&gt;""),IF(INDEX(Data!$M:$M,$L79)="","—",INDEX(Data!$M:$M,$L79)),"")</f>
         <v/>
       </c>
-      <c r="F79" s="21">
+      <c r="G79" s="21">
         <f>IF(AND(ISNUMBER($L79),$L79&lt;&gt;""),IF(INDEX(Data!$N:$N,$L79)="","—",INDEX(Data!$N:$N,$L79)),"")</f>
         <v/>
       </c>
-      <c r="G79" s="22">
+      <c r="H79" s="22">
         <f>IF(AND(ISNUMBER($L79),$L79&lt;&gt;""),IF(INDEX(Data!$Q:$Q,$L79)="","—",INDEX(Data!$Q:$Q,$L79)),"")</f>
         <v/>
       </c>
-      <c r="H79" s="23">
+      <c r="I79" s="23">
         <f>IF(AND(ISNUMBER($L79),$L79&lt;&gt;""),INDEX(Data!$E:$E,$L79),"")</f>
         <v/>
       </c>
-      <c r="I79" s="23">
+      <c r="J79" s="23">
         <f>IF(AND(ISNUMBER($L79),$L79&lt;&gt;""),INDEX(Data!$F:$F,$L79),"")</f>
         <v/>
       </c>
@@ -3792,22 +4078,22 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="F1:J1"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="A7:J7"/>
   </mergeCells>
-  <conditionalFormatting sqref="F10:G79">
+  <conditionalFormatting sqref="G10:H79">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
-      <formula>AND(ISNUMBER($F10),$F10=0)</formula>
+      <formula>AND(ISNUMBER($G10),$G10=0)</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
-      <formula>AND(ISNUMBER($F10),ABS($F10)&gt;=10)</formula>
+      <formula>AND(ISNUMBER($G10),ABS($G10)&gt;=10)</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
-      <formula>AND(ISNUMBER($F10),ABS($F10)&gt;=5)</formula>
+      <formula>AND(ISNUMBER($G10),ABS($G10)&gt;=5)</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="1">
-      <formula>AND(ISNUMBER($F10),ABS($F10)&gt;=1)</formula>
+      <formula>AND(ISNUMBER($G10),ABS($G10)&gt;=1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -13340,7 +13626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -13404,119 +13690,126 @@
     <row r="10">
       <c r="A10" s="27" t="inlineStr">
         <is>
-          <t>Closing — what was counted on the trading day named at the top.</t>
+          <t>Added — packs put onto the shelf since that opening count, from the restock records. Several restocks in the same period are summed.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>Sold (counted) — Opening minus Closing. What the shelf says went out.</t>
+          <t>Closing — what was counted on the trading day named at the top.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>Sold (POS) — what the till says it sold, from the imported sales report.</t>
+          <t>Sold (counted) — Opening plus Added minus Closing. What the shelf says went out.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>Variance — Sold (counted) minus Sold (POS), straight from the database view. It is not recalculated here, so it cannot drift from what the system believes.</t>
+          <t>Sold (POS) — what the till says it sold, from the imported sales report.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  positive — more left the shelf than the till sold: shrinkage, a miscount, or stock put out and not recorded.</t>
+          <t>Variance — Sold (counted) minus Sold (POS), straight from the database view. It is not recalculated here, so it cannot drift from what the system believes.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  negative — the till sold more than the shelf lost: usually a delivery.</t>
+          <t xml:space="preserve">  positive — more left the shelf than the till sold: shrinkage, a miscount, or stock put out and not recorded.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  an em dash — not known, not zero. Either no POS sales are loaded for that day, or it is the first count of that product and there is no opening to sell down from.</t>
+          <t xml:space="preserve">  negative — the till sold more than the shelf lost: usually a delivery.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
         <is>
+          <t xml:space="preserve">  an em dash — not known, not zero. Either no POS sales are loaded for that day, or it is the first count of that product and there is no opening to sell down from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
           <t>Variance RM — the variance valued at the price that day's report printed, falling back to the product list price. Blank means neither is known.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>Trends</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Variance by product over the last 14 counted days, sorted by how many days each product was off before how large the gap was. That ordering is the point: five nights of one pack is a leak worth chasing, one night of five packs is an event. The leak sits at the top. Anything older than 14 days is still on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="27" t="inlineStr"/>
-    </row>
     <row r="22">
-      <c r="A22" s="28" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>Two things that will skew variance</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="27" t="inlineStr">
-        <is>
-          <t>Deliveries are not recorded. The count screen collects one number per product and no longer captures stock added during the day, so add_in is always zero. On any day stock went onto the shelf, Sold (counted) understates what was sold and the day reads as negative variance. That column is deliberately not shown here — it would be a column of zeros implying something was checked.</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
         <is>
+          <t>Deliveries have to be recorded to count. The count screen collects one number per product and does not capture stock put out during the day; that is what the Restock screen is for, and what the Added column shows. A delivery nobody recorded still reads as negative variance, because as far as the shelf is concerned the packs appeared from nowhere. Check Added before believing a large negative day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
           <t>Counts must be consecutive. Opening is the previous submitted count's closing, whatever date that was. Check "Opening from" before believing a large variance.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="27" t="inlineStr"/>
-    </row>
     <row r="26">
-      <c r="A26" s="28" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>Refreshing</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="27" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>Data &gt; Refresh All, or just open the file if refresh-on-open is ticked. The rows come from the database through the query named Counts; the sheets are formulas on top of them, so new days and new products appear without anything being edited.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="27" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>The Data and Calc sheets are hidden. Data is the query's landing zone and Calc holds the working-out. Neither should be edited by hand: Data is overwritten on every refresh, and Calc is what Daily and Trends read.</t>
         </is>
